--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-fix-core-gpt\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.36-e08\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A137AD5-4E9C-4A74-9C12-E167CE1B38C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF1E34C-BE92-4D2C-88FB-E9FF413B65EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1078,10 +1078,10 @@
     <t>AMS</t>
   </si>
   <si>
-    <t>CUST-CE-TEST</t>
+    <t>CUST-CE-JCYL-TEST</t>
   </si>
   <si>
-    <t>Comunidad Educacion</t>
+    <t>Consejeria Educacion JCyL</t>
   </si>
   <si>
     <t>SLFC 20251160543</t>
@@ -1093,19 +1093,19 @@
     <t>E92001</t>
   </si>
   <si>
-    <t>PM AT Test</t>
+    <t>PM AT Test No Productivo</t>
   </si>
   <si>
     <t>E92002</t>
   </si>
   <si>
-    <t>Practice Leader AT Test</t>
+    <t>Practice Leader AT Test No Productivo</t>
   </si>
   <si>
     <t>E92003</t>
   </si>
   <si>
-    <t>Sales Manager AT Test</t>
+    <t>Sales Manager AT Test No Productivo</t>
   </si>
   <si>
     <t>E92012</t>
@@ -1126,7 +1126,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>Generado por RPA: 2026-05-11 09:11:46 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=7 | Datos SAP/SF del ejemplo: valores de prueba hardcodeados para validacion. | Revisar: campos externos, intercompany y planificacion.</t>
+    <t>Generado por RPA: 2026-05-11 10:20:45 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual.</t>
   </si>
 </sst>
 </file>
@@ -3075,13 +3075,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3091,9 +3084,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -7646,12 +7646,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="185">
-        <f>DATE(IF(EXACT(MONTH(EDATE(C5,0)),"12"),YEAR(C5)+1,YEAR(C5)),MONTH(EDATE(C5,1)),1)</f>
-        <v>46174</v>
+        <v>46022</v>
       </c>
       <c r="D6" s="63">
-        <f>DATE(YEAR(C6),MONTH(C6),1)</f>
-        <v>46174</v>
+        <v>46022</v>
       </c>
       <c r="E6" s="60"/>
       <c r="F6" s="67"/>
@@ -9019,7 +9017,7 @@
       </c>
       <c r="D4" s="315"/>
       <c r="E4" s="22"/>
-      <c r="F4" s="328" t="s">
+      <c r="F4" s="332" t="s">
         <v>240</v>
       </c>
       <c r="G4" s="333"/>
@@ -9032,26 +9030,26 @@
       <c r="J4" s="228" t="s">
         <v>243</v>
       </c>
-      <c r="K4" s="328" t="s">
+      <c r="K4" s="332" t="s">
         <v>244</v>
       </c>
-      <c r="L4" s="328"/>
-      <c r="M4" s="328"/>
-      <c r="N4" s="328"/>
+      <c r="L4" s="332"/>
+      <c r="M4" s="332"/>
+      <c r="N4" s="332"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="327" t="s">
+      <c r="C5" s="330" t="s">
         <v>246</v>
       </c>
-      <c r="D5" s="327"/>
+      <c r="D5" s="330"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="327" t="s">
+      <c r="F5" s="330" t="s">
         <v>247</v>
       </c>
-      <c r="G5" s="327"/>
+      <c r="G5" s="330"/>
       <c r="H5" s="230">
         <v>0.5</v>
       </c>
@@ -9061,24 +9059,24 @@
       <c r="J5" s="289" t="s">
         <v>246</v>
       </c>
-      <c r="K5" s="327"/>
-      <c r="L5" s="327"/>
-      <c r="M5" s="327"/>
-      <c r="N5" s="327"/>
+      <c r="K5" s="330"/>
+      <c r="L5" s="330"/>
+      <c r="M5" s="330"/>
+      <c r="N5" s="330"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="77" t="s">
         <v>248</v>
       </c>
-      <c r="C6" s="327" t="s">
+      <c r="C6" s="330" t="s">
         <v>249</v>
       </c>
-      <c r="D6" s="327"/>
+      <c r="D6" s="330"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="327" t="s">
+      <c r="F6" s="330" t="s">
         <v>250</v>
       </c>
-      <c r="G6" s="327"/>
+      <c r="G6" s="330"/>
       <c r="H6" s="230">
         <v>0.1</v>
       </c>
@@ -9086,26 +9084,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="289"/>
-      <c r="K6" s="327"/>
-      <c r="L6" s="327"/>
-      <c r="M6" s="327"/>
-      <c r="N6" s="327"/>
+      <c r="K6" s="330"/>
+      <c r="L6" s="330"/>
+      <c r="M6" s="330"/>
+      <c r="N6" s="330"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="C7" s="332">
+      <c r="C7" s="331">
         <v>10000</v>
       </c>
-      <c r="D7" s="332"/>
+      <c r="D7" s="331"/>
       <c r="E7" s="229" t="s">
         <v>252</v>
       </c>
-      <c r="F7" s="327" t="s">
+      <c r="F7" s="330" t="s">
         <v>253</v>
       </c>
-      <c r="G7" s="327"/>
+      <c r="G7" s="330"/>
       <c r="H7" s="230">
         <v>0.2</v>
       </c>
@@ -9113,18 +9111,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="289"/>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
+      <c r="K7" s="330"/>
+      <c r="L7" s="330"/>
+      <c r="M7" s="330"/>
+      <c r="N7" s="330"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="327" t="s">
+      <c r="F8" s="330" t="s">
         <v>254</v>
       </c>
-      <c r="G8" s="327"/>
+      <c r="G8" s="330"/>
       <c r="H8" s="230">
         <v>0.1</v>
       </c>
@@ -9132,18 +9130,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="289"/>
-      <c r="K8" s="327"/>
-      <c r="L8" s="327"/>
-      <c r="M8" s="327"/>
-      <c r="N8" s="327"/>
+      <c r="K8" s="330"/>
+      <c r="L8" s="330"/>
+      <c r="M8" s="330"/>
+      <c r="N8" s="330"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="22"/>
       <c r="E9" s="56"/>
-      <c r="F9" s="327" t="s">
+      <c r="F9" s="330" t="s">
         <v>255</v>
       </c>
-      <c r="G9" s="327"/>
+      <c r="G9" s="330"/>
       <c r="H9" s="230">
         <v>0.1</v>
       </c>
@@ -9151,10 +9149,10 @@
         <v>1000</v>
       </c>
       <c r="J9" s="289"/>
-      <c r="K9" s="327"/>
-      <c r="L9" s="327"/>
-      <c r="M9" s="327"/>
-      <c r="N9" s="327"/>
+      <c r="K9" s="330"/>
+      <c r="L9" s="330"/>
+      <c r="M9" s="330"/>
+      <c r="N9" s="330"/>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
@@ -10240,12 +10238,12 @@
       <c r="W45" s="21"/>
     </row>
     <row r="46" spans="2:23" s="89" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="329" t="s">
+      <c r="B46" s="327" t="s">
         <v>235</v>
       </c>
-      <c r="C46" s="329"/>
-      <c r="D46" s="329"/>
-      <c r="E46" s="329"/>
+      <c r="C46" s="327"/>
+      <c r="D46" s="327"/>
+      <c r="E46" s="327"/>
       <c r="F46" s="219">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10409,16 +10407,16 @@
       <c r="R55" s="24"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="330" t="s">
+      <c r="B56" s="328" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="331"/>
-      <c r="D56" s="331"/>
-      <c r="E56" s="331"/>
-      <c r="F56" s="331"/>
-      <c r="G56" s="331"/>
-      <c r="H56" s="331"/>
-      <c r="I56" s="331"/>
+      <c r="C56" s="329"/>
+      <c r="D56" s="329"/>
+      <c r="E56" s="329"/>
+      <c r="F56" s="329"/>
+      <c r="G56" s="329"/>
+      <c r="H56" s="329"/>
+      <c r="I56" s="329"/>
       <c r="J56" s="173"/>
       <c r="K56" s="173"/>
       <c r="L56" s="173"/>
@@ -10432,6 +10430,16 @@
   </sheetData>
   <autoFilter ref="B12:E12" xr:uid="{F0215733-3491-41E7-AEDA-44D9E214180D}"/>
   <mergeCells count="19">
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="C4:D4"/>
@@ -10441,16 +10449,6 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C10">
@@ -16081,112 +16079,112 @@
         <v>32.840000000000003</v>
       </c>
       <c r="S7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="T7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="U7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="V7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="W7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="X7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="Y7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="Z7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="AA7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="AB7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="AC7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="AD7">
-        <v>32.840000000000003</v>
+        <v>33.825200000000002</v>
       </c>
       <c r="AE7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AF7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AG7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AH7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AI7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AJ7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AK7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AL7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AM7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AN7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AO7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AP7">
-        <v>32.840000000000003</v>
+        <v>34.839956000000001</v>
       </c>
       <c r="AQ7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AR7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AS7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AT7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AU7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AV7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AW7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AX7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AY7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="AZ7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="BA7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="BB7">
-        <v>32.840000000000003</v>
+        <v>35.885154679999999</v>
       </c>
       <c r="BC7" s="265"/>
       <c r="BD7" s="265"/>
@@ -16230,148 +16228,148 @@
         <v>92</v>
       </c>
       <c r="G8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="H8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="I8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="J8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="K8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="L8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="M8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="N8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="O8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="P8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="Q8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="R8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="S8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="T8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="U8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="V8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="W8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="X8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="Y8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="Z8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AA8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AB8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AC8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AD8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AE8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AF8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AG8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AH8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AI8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AJ8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AK8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AL8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AM8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AN8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AO8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AP8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AQ8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AR8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AS8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AT8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AU8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AV8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AW8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AX8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AY8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="AZ8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="BA8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="BB8">
-        <v>44.347014925373138</v>
+        <v>44.790488927572149</v>
       </c>
       <c r="BC8" s="266"/>
       <c r="BD8" s="266"/>
@@ -16451,112 +16449,112 @@
         <v>15.17</v>
       </c>
       <c r="S9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="T9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="U9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="V9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="W9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="X9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="Y9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="Z9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="AA9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="AB9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="AC9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="AD9">
-        <v>15.17</v>
+        <v>15.625100000000002</v>
       </c>
       <c r="AE9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AF9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AG9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AH9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AI9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AJ9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AK9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AL9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AM9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AN9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AO9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AP9">
-        <v>15.17</v>
+        <v>16.093852999999999</v>
       </c>
       <c r="AQ9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AR9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AS9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AT9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AU9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AV9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AW9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AX9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AY9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="AZ9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="BA9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="BB9">
-        <v>15.17</v>
+        <v>16.576668590000001</v>
       </c>
       <c r="BC9" s="265"/>
       <c r="BD9" s="265"/>
@@ -16600,148 +16598,148 @@
         <v>92</v>
       </c>
       <c r="G10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="H10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="I10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="J10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="K10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="L10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="M10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="N10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="O10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="P10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="Q10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="R10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="S10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="T10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="U10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="V10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="W10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="X10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="Y10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="Z10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AA10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AB10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AC10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AD10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AE10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AF10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AG10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AH10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AI10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AJ10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AK10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AL10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AM10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AN10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AO10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AP10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AQ10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AR10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AS10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AT10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AU10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AV10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AW10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AX10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AY10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="AZ10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="BA10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="BB10">
-        <v>20.485505166475317</v>
+        <v>20.690361997956153</v>
       </c>
       <c r="BC10" s="266"/>
       <c r="BD10" s="266"/>
@@ -16821,112 +16819,112 @@
         <v>20</v>
       </c>
       <c r="S11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="T11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="U11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="V11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="W11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="X11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="Y11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="Z11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="AA11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="AB11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="AC11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="AD11">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="AE11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AF11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AG11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AH11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AI11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AJ11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AK11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AL11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AM11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AN11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AO11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>21.218</v>
       </c>
       <c r="AQ11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AR11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AS11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AT11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AU11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AV11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AW11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AX11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AY11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="BA11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="BB11">
-        <v>20</v>
+        <v>21.85454</v>
       </c>
       <c r="BC11" s="265"/>
       <c r="BD11" s="265"/>
@@ -16970,148 +16968,148 @@
         <v>92</v>
       </c>
       <c r="G12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="H12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="I12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="J12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="K12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="L12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="M12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="N12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="O12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="P12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="Q12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="R12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="S12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="T12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="U12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="V12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="W12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="X12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="Y12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="Z12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AA12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AB12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AC12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AD12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AE12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AF12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AG12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AH12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AI12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AJ12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AK12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AL12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AM12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AN12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AO12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AP12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AQ12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AR12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AS12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AT12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AU12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AV12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AW12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AX12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AY12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="AZ12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="BA12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="BB12">
-        <v>27.009374999999999</v>
+        <v>27.279471096621165</v>
       </c>
       <c r="BC12" s="266"/>
       <c r="BD12" s="266"/>
@@ -20666,7 +20664,7 @@
       <c r="I5" s="113"/>
       <c r="J5" s="114">
         <f>F5-SUM(F40:BO41)</f>
-        <v>15651.160000000207</v>
+        <v>2.7856598026119173E-3</v>
       </c>
       <c r="K5" s="99"/>
       <c r="L5" s="275" t="s">
@@ -20675,7 +20673,7 @@
       <c r="M5" s="113"/>
       <c r="N5" s="114">
         <f>-(pedidobaselineactual-SUM(H44:BO44)-SUM(H62:BO62)-SUM(H78:BO78))</f>
-        <v>-4604.000000000291</v>
+        <v>0</v>
       </c>
       <c r="O5" s="229"/>
       <c r="P5" s="229"/>
@@ -20709,27 +20707,27 @@
       <c r="G7" s="109"/>
       <c r="H7" s="116" t="str">
         <f>IF(H8&gt;EOMONTH(FIN,0),"Fin",IF(H8&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="I7" s="116" t="str">
         <f t="shared" ref="I7:BO7" si="0">IF(I8&gt;EOMONTH(FIN,0),"Fin",IF(I8&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="J7" s="116" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="K7" s="116" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="L7" s="116" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="M7" s="116" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="N7" s="116" t="str">
         <f t="shared" si="0"/>
@@ -24390,147 +24388,147 @@
       </c>
       <c r="T40" s="120" cm="1">
         <f t="array" ref="T40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,T$10:T$39,Resources!S7:S36)+T42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="U40" s="120" cm="1">
         <f t="array" ref="U40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,U$10:U$39,Resources!T7:T36)+U42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="V40" s="120" cm="1">
         <f t="array" ref="V40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,V$10:V$39,Resources!U7:U36)+V42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="W40" s="120" cm="1">
         <f t="array" ref="W40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,W$10:W$39,Resources!V7:V36)+W42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="X40" s="120" cm="1">
         <f t="array" ref="X40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,X$10:X$39,Resources!W7:W36)+X42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="Y40" s="120" cm="1">
         <f t="array" ref="Y40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,Y$10:Y$39,Resources!X7:X36)+Y42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="Z40" s="120" cm="1">
         <f t="array" ref="Z40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,Z$10:Z$39,Resources!Y7:Y36)+Z42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="AA40" s="120" cm="1">
         <f t="array" ref="AA40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AA$10:AA$39,Resources!Z7:Z36)+AA42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="AB40" s="120" cm="1">
         <f t="array" ref="AB40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AB$10:AB$39,Resources!AA7:AA36)+AB42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="AC40" s="120" cm="1">
         <f t="array" ref="AC40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AC$10:AC$39,Resources!AB7:AB36)+AC42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="AD40" s="120" cm="1">
         <f t="array" ref="AD40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AD$10:AD$39,Resources!AC7:AC36)+AD42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="AE40" s="120" cm="1">
         <f t="array" ref="AE40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AE$10:AE$39,Resources!AD7:AD36)+AE42</f>
-        <v>7102.7849999999999</v>
+        <v>7315.8685500000001</v>
       </c>
       <c r="AF40" s="120" cm="1">
         <f t="array" ref="AF40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AF$10:AF$39,Resources!AE7:AE36)+AF42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AG40" s="120" cm="1">
         <f t="array" ref="AG40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AG$10:AG$39,Resources!AF7:AF36)+AG42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AH40" s="120" cm="1">
         <f t="array" ref="AH40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AH$10:AH$39,Resources!AG7:AG36)+AH42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AI40" s="120" cm="1">
         <f t="array" ref="AI40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AI$10:AI$39,Resources!AH7:AH36)+AI42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AJ40" s="120" cm="1">
         <f t="array" ref="AJ40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AJ$10:AJ$39,Resources!AI7:AI36)+AJ42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AK40" s="120" cm="1">
         <f t="array" ref="AK40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AK$10:AK$39,Resources!AJ7:AJ36)+AK42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AL40" s="120" cm="1">
         <f t="array" ref="AL40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AL$10:AL$39,Resources!AK7:AK36)+AL42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AM40" s="120" cm="1">
         <f t="array" ref="AM40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AM$10:AM$39,Resources!AL7:AL36)+AM42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AN40" s="120" cm="1">
         <f t="array" ref="AN40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AN$10:AN$39,Resources!AM7:AM36)+AN42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AO40" s="120" cm="1">
         <f t="array" ref="AO40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AO$10:AO$39,Resources!AN7:AN36)+AO42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AP40" s="120" cm="1">
         <f t="array" ref="AP40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AP$10:AP$39,Resources!AO7:AO36)+AP42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AQ40" s="120" cm="1">
         <f t="array" ref="AQ40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AQ$10:AQ$39,Resources!AP7:AP36)+AQ42</f>
-        <v>7102.7849999999999</v>
+        <v>7535.3446064999989</v>
       </c>
       <c r="AR40" s="120" cm="1">
         <f t="array" ref="AR40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AR$10:AR$39,Resources!AQ7:AQ36)+AR42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AS40" s="120" cm="1">
         <f t="array" ref="AS40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AS$10:AS$39,Resources!AR7:AR36)+AS42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AT40" s="120" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AT$10:AT$39,Resources!AS7:AS36)+AT42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AU40" s="120" cm="1">
         <f t="array" ref="AU40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AU$10:AU$39,Resources!AT7:AT36)+AU42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AV40" s="120" cm="1">
         <f t="array" ref="AV40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AV$10:AV$39,Resources!AU7:AU36)+AV42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AW40" s="120" cm="1">
         <f t="array" ref="AW40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AW$10:AW$39,Resources!AV7:AV36)+AW42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AX40" s="120" cm="1">
         <f t="array" ref="AX40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AX$10:AX$39,Resources!AW7:AW36)+AX42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AY40" s="120" cm="1">
         <f t="array" ref="AY40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AY$10:AY$39,Resources!AX7:AX36)+AY42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="AZ40" s="120" cm="1">
         <f t="array" ref="AZ40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,AZ$10:AZ$39,Resources!AY7:AY36)+AZ42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="BA40" s="120" cm="1">
         <f t="array" ref="BA40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,BA$10:BA$39,Resources!AZ7:AZ36)+BA42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="BB40" s="120" cm="1">
         <f t="array" ref="BB40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,BB$10:BB$39,Resources!BA7:BA36)+BB42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="BC40" s="120" cm="1">
         <f t="array" ref="BC40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,BC$10:BC$39,Resources!BB7:BB36)+BC42</f>
-        <v>7102.7849999999999</v>
+        <v>7761.4049446950003</v>
       </c>
       <c r="BD40" s="120" cm="1">
         <f t="array" ref="BD40">SUMPRODUCT(($D$10:$D$39="NO")*1,($G$10:$G$39="Horas Reales")*1,BD$10:BD$39,Resources!BC7:BC36)+BD42</f>
@@ -24982,195 +24980,195 @@
       <c r="G44" s="120"/>
       <c r="H44" s="282" cm="1">
         <f t="array" ref="H44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,H$10:H$39,Resources!G7:G36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="I44" s="282" cm="1">
         <f t="array" ref="I44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,I$10:I$39,Resources!H7:H36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="J44" s="282" cm="1">
         <f t="array" ref="J44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,J$10:J$39,Resources!I7:I36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="K44" s="282" cm="1">
         <f t="array" ref="K44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,K$10:K$39,Resources!J7:J36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="L44" s="282" cm="1">
         <f t="array" ref="L44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,L$10:L$39,Resources!K7:K36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="M44" s="282" cm="1">
         <f t="array" ref="M44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,M$10:M$39,Resources!L7:L36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="N44" s="282" cm="1">
         <f t="array" ref="N44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,N$10:N$39,Resources!M7:M36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="O44" s="282" cm="1">
         <f t="array" ref="O44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,O$10:O$39,Resources!N7:N36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="P44" s="282" cm="1">
         <f t="array" ref="P44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,P$10:P$39,Resources!O7:O36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="Q44" s="282" cm="1">
         <f t="array" ref="Q44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,Q$10:Q$39,Resources!P7:P36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="R44" s="282" cm="1">
         <f t="array" ref="R44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,R$10:R$39,Resources!Q7:Q36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="S44" s="282" cm="1">
         <f t="array" ref="S44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,S$10:S$39,Resources!R7:R36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="T44" s="282" cm="1">
         <f t="array" ref="T44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,T$10:T$39,Resources!S7:S36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="U44" s="282" cm="1">
         <f t="array" ref="U44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,U$10:U$39,Resources!T7:T36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="V44" s="282" cm="1">
         <f t="array" ref="V44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,V$10:V$39,Resources!U7:U36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="W44" s="282" cm="1">
         <f t="array" ref="W44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,W$10:W$39,Resources!V7:V36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="X44" s="282" cm="1">
         <f t="array" ref="X44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,X$10:X$39,Resources!W7:W36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="Y44" s="282" cm="1">
         <f t="array" ref="Y44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,Y$10:Y$39,Resources!X7:X36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="Z44" s="282" cm="1">
         <f t="array" ref="Z44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,Z$10:Z$39,Resources!Y7:Y36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AA44" s="282" cm="1">
         <f t="array" ref="AA44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AA$10:AA$39,Resources!Z7:Z36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AB44" s="282" cm="1">
         <f t="array" ref="AB44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AB$10:AB$39,Resources!AA7:AA36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AC44" s="282" cm="1">
         <f t="array" ref="AC44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AC$10:AC$39,Resources!AB7:AB36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AD44" s="282" cm="1">
         <f t="array" ref="AD44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AD$10:AD$39,Resources!AC7:AC36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AE44" s="282" cm="1">
         <f t="array" ref="AE44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AE$10:AE$39,Resources!AD7:AD36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AF44" s="282" cm="1">
         <f t="array" ref="AF44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AF$10:AF$39,Resources!AE7:AE36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AG44" s="282" cm="1">
         <f t="array" ref="AG44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AG$10:AG$39,Resources!AF7:AF36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AH44" s="282" cm="1">
         <f t="array" ref="AH44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AH$10:AH$39,Resources!AG7:AG36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AI44" s="282" cm="1">
         <f t="array" ref="AI44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AI$10:AI$39,Resources!AH7:AH36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AJ44" s="282" cm="1">
         <f t="array" ref="AJ44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AJ$10:AJ$39,Resources!AI7:AI36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AK44" s="282" cm="1">
         <f t="array" ref="AK44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AK$10:AK$39,Resources!AJ7:AJ36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AL44" s="282" cm="1">
         <f t="array" ref="AL44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AL$10:AL$39,Resources!AK7:AK36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AM44" s="282" cm="1">
         <f t="array" ref="AM44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AM$10:AM$39,Resources!AL7:AL36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AN44" s="282" cm="1">
         <f t="array" ref="AN44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AN$10:AN$39,Resources!AM7:AM36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AO44" s="282" cm="1">
         <f t="array" ref="AO44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AO$10:AO$39,Resources!AN7:AN36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AP44" s="282" cm="1">
         <f t="array" ref="AP44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AP$10:AP$39,Resources!AO7:AO36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AQ44" s="282" cm="1">
         <f t="array" ref="AQ44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AQ$10:AQ$39,Resources!AP7:AP36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AR44" s="282" cm="1">
         <f t="array" ref="AR44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AR$10:AR$39,Resources!AQ7:AQ36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AS44" s="282" cm="1">
         <f t="array" ref="AS44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AS$10:AS$39,Resources!AR7:AR36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AT44" s="282" cm="1">
         <f t="array" ref="AT44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AT$10:AT$39,Resources!AS7:AS36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AU44" s="282" cm="1">
         <f t="array" ref="AU44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AU$10:AU$39,Resources!AT7:AT36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AV44" s="282" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AV$10:AV$39,Resources!AU7:AU36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AW44" s="282" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AW$10:AW$39,Resources!AV7:AV36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AX44" s="282" cm="1">
         <f t="array" ref="AX44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AX$10:AX$39,Resources!AW7:AW36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AY44" s="282" cm="1">
         <f t="array" ref="AY44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AY$10:AY$39,Resources!AX7:AX36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AZ44" s="282" cm="1">
         <f t="array" ref="AZ44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AZ$10:AZ$39,Resources!AY7:AY36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="BA44" s="282" cm="1">
         <f t="array" ref="BA44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BA$10:BA$39,Resources!AZ7:AZ36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="BB44" s="282" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BB$10:BB$39,Resources!BA7:BA36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="BC44" s="282" cm="1">
         <f t="array" ref="BC44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BC$10:BC$39,Resources!BB7:BB36)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="BD44" s="282" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BD$10:BD$39,Resources!BC7:BC36)</f>
@@ -29517,7 +29515,7 @@
       <c r="L2" s="294"/>
       <c r="M2" s="168">
         <f>'Cost Planning'!N5</f>
-        <v>-4604.000000000291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:77" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -29533,27 +29531,27 @@
       <c r="D4" s="143"/>
       <c r="E4" s="144" t="str">
         <f t="shared" ref="E4:BL4" si="0">IF(E5&gt;EOMONTH(FIN,0),"Fin",IF(E5&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="F4" s="144" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="G4" s="144" t="str">
         <f>IF(G5&gt;EOMONTH(FIN,0),"Fin",IF(G5&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="H4" s="144" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="I4" s="144" t="str">
         <f>IF(I5&gt;EOMONTH(FIN,0),"Fin",IF(I5&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="J4" s="144" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="K4" s="144" t="str">
         <f t="shared" si="0"/>
@@ -31797,7 +31795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B13" s="298" t="s">
         <v>65</v>
       </c>
@@ -32821,195 +32819,195 @@
       <c r="D18" s="150"/>
       <c r="E18" s="150">
         <f>'Cost Planning'!H44+'Cost Planning'!H62+'Cost Planning'!H78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="F18" s="150">
         <f>'Cost Planning'!I44+'Cost Planning'!I62+'Cost Planning'!I78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="G18" s="150">
         <f>'Cost Planning'!J44+'Cost Planning'!J62+'Cost Planning'!J78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="H18" s="150">
         <f>'Cost Planning'!K44+'Cost Planning'!K62+'Cost Planning'!K78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="I18" s="150">
         <f>'Cost Planning'!L44+'Cost Planning'!L62+'Cost Planning'!L78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="J18" s="150">
         <f>'Cost Planning'!M44+'Cost Planning'!M62+'Cost Planning'!M78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="K18" s="150">
         <f>'Cost Planning'!N44+'Cost Planning'!N62+'Cost Planning'!N78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="L18" s="150">
         <f>'Cost Planning'!O44+'Cost Planning'!O62+'Cost Planning'!O78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="M18" s="150">
         <f>'Cost Planning'!P44+'Cost Planning'!P62+'Cost Planning'!P78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="N18" s="150">
         <f>'Cost Planning'!Q44+'Cost Planning'!Q62+'Cost Planning'!Q78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="O18" s="150">
         <f>'Cost Planning'!R44+'Cost Planning'!R62+'Cost Planning'!R78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="P18" s="150">
         <f>'Cost Planning'!S44+'Cost Planning'!S62+'Cost Planning'!S78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="Q18" s="150">
         <f>'Cost Planning'!T44+'Cost Planning'!T62+'Cost Planning'!T78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="R18" s="150">
         <f>'Cost Planning'!U44+'Cost Planning'!U62+'Cost Planning'!U78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="S18" s="150">
         <f>'Cost Planning'!V44+'Cost Planning'!V62+'Cost Planning'!V78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="T18" s="150">
         <f>'Cost Planning'!W44+'Cost Planning'!W62+'Cost Planning'!W78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="U18" s="150">
         <f>'Cost Planning'!X44+'Cost Planning'!X62+'Cost Planning'!X78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="V18" s="150">
         <f>'Cost Planning'!Y44+'Cost Planning'!Y62+'Cost Planning'!Y78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="W18" s="150">
         <f>'Cost Planning'!Z44+'Cost Planning'!Z62+'Cost Planning'!Z78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="X18" s="150">
         <f>'Cost Planning'!AA44+'Cost Planning'!AA62+'Cost Planning'!AA78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="Y18" s="150">
         <f>'Cost Planning'!AB44+'Cost Planning'!AB62+'Cost Planning'!AB78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="Z18" s="150">
         <f>'Cost Planning'!AC44+'Cost Planning'!AC62+'Cost Planning'!AC78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AA18" s="150">
         <f>'Cost Planning'!AD44+'Cost Planning'!AD62+'Cost Planning'!AD78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AB18" s="150">
         <f>'Cost Planning'!AE44+'Cost Planning'!AE62+'Cost Planning'!AE78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AC18" s="150">
         <f>'Cost Planning'!AF44+'Cost Planning'!AF62+'Cost Planning'!AF78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AD18" s="150">
         <f>'Cost Planning'!AG44+'Cost Planning'!AG62+'Cost Planning'!AG78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AE18" s="150">
         <f>'Cost Planning'!AH44+'Cost Planning'!AH62+'Cost Planning'!AH78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AF18" s="150">
         <f>'Cost Planning'!AI44+'Cost Planning'!AI62+'Cost Planning'!AI78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AG18" s="150">
         <f>'Cost Planning'!AJ44+'Cost Planning'!AJ62+'Cost Planning'!AJ78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AH18" s="150">
         <f>'Cost Planning'!AK44+'Cost Planning'!AK62+'Cost Planning'!AK78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AI18" s="150">
         <f>'Cost Planning'!AL44+'Cost Planning'!AL62+'Cost Planning'!AL78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AJ18" s="150">
         <f>'Cost Planning'!AM44+'Cost Planning'!AM62+'Cost Planning'!AM78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AK18" s="150">
         <f>'Cost Planning'!AN44+'Cost Planning'!AN62+'Cost Planning'!AN78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AL18" s="150">
         <f>'Cost Planning'!AO44+'Cost Planning'!AO62+'Cost Planning'!AO78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AM18" s="150">
         <f>'Cost Planning'!AP44+'Cost Planning'!AP62+'Cost Planning'!AP78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AN18" s="150">
         <f>'Cost Planning'!AQ44+'Cost Planning'!AQ62+'Cost Planning'!AQ78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AO18" s="150">
         <f>'Cost Planning'!AR44+'Cost Planning'!AR62+'Cost Planning'!AR78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AP18" s="150">
         <f>'Cost Planning'!AS44+'Cost Planning'!AS62+'Cost Planning'!AS78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AQ18" s="150">
         <f>'Cost Planning'!AT44+'Cost Planning'!AT62+'Cost Planning'!AT78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AR18" s="150">
         <f>'Cost Planning'!AU44+'Cost Planning'!AU62+'Cost Planning'!AU78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AS18" s="150">
         <f>'Cost Planning'!AV44+'Cost Planning'!AV62+'Cost Planning'!AV78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AT18" s="150">
         <f>'Cost Planning'!AW44+'Cost Planning'!AW62+'Cost Planning'!AW78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AU18" s="150">
         <f>'Cost Planning'!AX44+'Cost Planning'!AX62+'Cost Planning'!AX78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AV18" s="150">
         <f>'Cost Planning'!AY44+'Cost Planning'!AY62+'Cost Planning'!AY78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AW18" s="150">
         <f>'Cost Planning'!AZ44+'Cost Planning'!AZ62+'Cost Planning'!AZ78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AX18" s="150">
         <f>'Cost Planning'!BA44+'Cost Planning'!BA62+'Cost Planning'!BA78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AY18" s="150">
         <f>'Cost Planning'!BB44+'Cost Planning'!BB62+'Cost Planning'!BB78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="AZ18" s="150">
         <f>'Cost Planning'!BC44+'Cost Planning'!BC62+'Cost Planning'!BC78</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="BA18" s="150">
         <f>'Cost Planning'!BD44+'Cost Planning'!BD62+'Cost Planning'!BD78</f>
@@ -33388,147 +33386,147 @@
       </c>
       <c r="Q20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="R20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="S20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="T20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="U20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="V20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="W20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7849999999889</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="X20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="Y20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="Z20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="AA20" s="152">
         <f t="shared" si="143"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="AB20" s="152">
         <f t="shared" si="106"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="AC20" s="152">
         <f t="shared" si="107"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AD20" s="152">
         <f t="shared" si="108"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AE20" s="152">
         <f t="shared" si="109"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AF20" s="152">
         <f t="shared" si="110"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AG20" s="152">
         <f t="shared" si="111"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AH20" s="152">
         <f t="shared" si="112"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AI20" s="152">
         <f t="shared" si="113"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AJ20" s="152">
         <f t="shared" si="114"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AK20" s="152">
         <f t="shared" si="115"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AL20" s="152">
         <f t="shared" si="116"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AM20" s="152">
         <f t="shared" si="117"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AN20" s="152">
         <f t="shared" si="118"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AO20" s="152">
         <f t="shared" si="119"/>
-        <v>7102.7850000000035</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AP20" s="152">
         <f t="shared" si="120"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AQ20" s="152">
         <f t="shared" si="121"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AR20" s="152">
         <f t="shared" si="122"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AS20" s="152">
         <f t="shared" si="123"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AT20" s="152">
         <f t="shared" si="124"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AU20" s="152">
         <f t="shared" si="125"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AV20" s="152">
         <f t="shared" si="126"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AW20" s="152">
         <f t="shared" si="127"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AX20" s="152">
         <f t="shared" si="128"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AY20" s="152">
         <f t="shared" si="129"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AZ20" s="152">
         <f t="shared" si="130"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="BA20" s="152">
         <f t="shared" si="131"/>
@@ -34659,147 +34657,147 @@
       </c>
       <c r="Q25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="R25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="S25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="T25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="U25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="V25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="W25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7849999999889</v>
+        <v>7315.8685499999992</v>
       </c>
       <c r="X25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="Y25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="Z25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="AA25" s="151">
         <f t="shared" si="148"/>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="AB25" s="151">
         <f>SUM(AB20:AB24)</f>
-        <v>7102.7850000000035</v>
+        <v>7315.8685500000138</v>
       </c>
       <c r="AC25" s="151">
         <f t="shared" ref="AC25:BL25" si="149">SUM(AC20:AC24)</f>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AD25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AE25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AF25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AG25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AH25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AI25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AJ25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AK25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AL25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AM25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AN25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7535.3446065000026</v>
       </c>
       <c r="AO25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7850000000035</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AP25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AQ25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AR25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AS25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AT25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AU25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AV25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AW25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AX25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AY25" s="151">
         <f t="shared" si="149"/>
-        <v>7102.7849999999744</v>
+        <v>7761.4049446950085</v>
       </c>
       <c r="AZ25" s="151">
         <f t="shared" si="149"/>
-        <v>10668.634999999975</v>
+        <v>11327.254944695009</v>
       </c>
       <c r="BA25" s="151">
         <f t="shared" si="149"/>
@@ -34858,195 +34856,195 @@
       <c r="D26" s="153"/>
       <c r="E26" s="153">
         <f>E18-E25</f>
-        <v>2488.7983333333323</v>
+        <v>2584.7150000000001</v>
       </c>
       <c r="F26" s="157">
         <f t="shared" ref="F26:Z26" si="150">F18-F25</f>
-        <v>2488.7983333333323</v>
+        <v>2584.7150000000001</v>
       </c>
       <c r="G26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333323</v>
+        <v>2584.7150000000001</v>
       </c>
       <c r="H26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333323</v>
+        <v>2584.7150000000001</v>
       </c>
       <c r="I26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="J26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="K26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="L26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="M26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="N26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="O26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="P26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2584.7149999999965</v>
       </c>
       <c r="Q26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="R26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="S26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="T26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="U26" s="157">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="V26" s="153">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="W26" s="153">
         <f t="shared" si="150"/>
-        <v>2488.7983333333432</v>
+        <v>2371.6314500000008</v>
       </c>
       <c r="X26" s="153">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314499999862</v>
       </c>
       <c r="Y26" s="153">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314499999862</v>
       </c>
       <c r="Z26" s="153">
         <f t="shared" si="150"/>
-        <v>2488.7983333333286</v>
+        <v>2371.6314499999862</v>
       </c>
       <c r="AA26" s="153">
         <f>AA18-AA25</f>
-        <v>2488.7983333333286</v>
+        <v>2371.6314499999862</v>
       </c>
       <c r="AB26" s="153">
         <f>AB18-AB25</f>
-        <v>2488.7983333333286</v>
+        <v>2371.6314499999862</v>
       </c>
       <c r="AC26" s="153">
         <f t="shared" ref="AC26:BL26" si="151">AC18-AC25</f>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AD26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AE26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AF26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AG26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AH26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AI26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AJ26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AK26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AL26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AM26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AN26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>2152.1553934999974</v>
       </c>
       <c r="AO26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333286</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AP26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AQ26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AR26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AS26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AT26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AU26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AV26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AW26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AX26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AY26" s="153">
         <f t="shared" si="151"/>
-        <v>2488.7983333333577</v>
+        <v>1926.0950553049915</v>
       </c>
       <c r="AZ26" s="153">
         <f t="shared" si="151"/>
-        <v>-1077.0516666666426</v>
+        <v>-1639.7549446950088</v>
       </c>
       <c r="BA26" s="153">
         <f t="shared" si="151"/>
@@ -35105,195 +35103,195 @@
       <c r="D27" s="154"/>
       <c r="E27" s="154">
         <f>IF(E18=0,0,(E18-SUM(E20,E21,E22,E23,E24))/E18)</f>
-        <v>0.25947731952493064</v>
+        <v>0.26680929032258066</v>
       </c>
       <c r="F27" s="154">
         <f t="shared" ref="F27:Z27" si="152">IF(F18=0,0,(F18-SUM(F20,F21,F22,F23,F24))/F18)</f>
-        <v>0.25947731952493064</v>
+        <v>0.26680929032258066</v>
       </c>
       <c r="G27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493064</v>
+        <v>0.26680929032258066</v>
       </c>
       <c r="H27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493064</v>
+        <v>0.26680929032258066</v>
       </c>
       <c r="I27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="J27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="K27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="L27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="M27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="N27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="O27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="P27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.26680929032258027</v>
       </c>
       <c r="Q27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="R27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="S27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="T27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="U27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="V27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="W27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493175</v>
+        <v>0.24481356903225815</v>
       </c>
       <c r="X27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225665</v>
       </c>
       <c r="Y27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225665</v>
       </c>
       <c r="Z27" s="154">
         <f t="shared" si="152"/>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225665</v>
       </c>
       <c r="AA27" s="154">
         <f>IF(AA18=0,0,(AA18-SUM(AA20,AA21,AA22,AA23,AA24))/AA18)</f>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225665</v>
       </c>
       <c r="AB27" s="154">
         <f>IF(AB18=0,0,(AB18-SUM(AB20,AB21,AB22,AB23,AB24))/AB18)</f>
-        <v>0.25947731952493025</v>
+        <v>0.24481356903225665</v>
       </c>
       <c r="AC27" s="154">
         <f t="shared" ref="AC27:BL27" si="153">IF(AC18=0,0,(AC18-SUM(AC20,AC21,AC22,AC23,AC24))/AC18)</f>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AD27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AE27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AF27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AG27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AH27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AI27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AJ27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AK27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AL27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AM27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AN27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.22215797610322555</v>
       </c>
       <c r="AO27" s="154">
         <f t="shared" si="153"/>
-        <v>0.25947731952493025</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AP27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AQ27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AR27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AS27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AT27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AU27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AV27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AW27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AX27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AY27" s="154">
         <f t="shared" si="153"/>
-        <v>0.2594773195249333</v>
+        <v>0.19882271538632171</v>
       </c>
       <c r="AZ27" s="154">
         <f t="shared" si="153"/>
-        <v>-0.11229133181000454</v>
+        <v>-0.1692650265491622</v>
       </c>
       <c r="BA27" s="154">
         <f t="shared" si="153"/>
@@ -35623,191 +35621,191 @@
       </c>
       <c r="E30" s="150">
         <f t="shared" ref="E30:AB30" ca="1" si="213">IF(E40,E40,D30+E18)</f>
-        <v>9591.5833333333321</v>
+        <v>9687.5</v>
       </c>
       <c r="F30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>19183.166666666664</v>
+        <v>19375</v>
       </c>
       <c r="G30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>28774.749999999996</v>
+        <v>29062.5</v>
       </c>
       <c r="H30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>38366.333333333328</v>
+        <v>38750</v>
       </c>
       <c r="I30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>47957.916666666657</v>
+        <v>48437.5</v>
       </c>
       <c r="J30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>57549.499999999985</v>
+        <v>58125</v>
       </c>
       <c r="K30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>67141.083333333314</v>
+        <v>67812.5</v>
       </c>
       <c r="L30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>76732.666666666642</v>
+        <v>77500</v>
       </c>
       <c r="M30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>86324.249999999971</v>
+        <v>87187.5</v>
       </c>
       <c r="N30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>95915.833333333299</v>
+        <v>96875</v>
       </c>
       <c r="O30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>105507.41666666663</v>
+        <v>106562.5</v>
       </c>
       <c r="P30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>115098.99999999996</v>
+        <v>116250</v>
       </c>
       <c r="Q30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>124690.58333333328</v>
+        <v>125937.5</v>
       </c>
       <c r="R30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>134282.16666666663</v>
+        <v>135625</v>
       </c>
       <c r="S30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>143873.74999999997</v>
+        <v>145312.5</v>
       </c>
       <c r="T30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>153465.33333333331</v>
+        <v>155000</v>
       </c>
       <c r="U30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>163056.91666666666</v>
+        <v>164687.5</v>
       </c>
       <c r="V30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>172648.5</v>
+        <v>174375</v>
       </c>
       <c r="W30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>182240.08333333334</v>
+        <v>184062.5</v>
       </c>
       <c r="X30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>191831.66666666669</v>
+        <v>193750</v>
       </c>
       <c r="Y30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>201423.25000000003</v>
+        <v>203437.5</v>
       </c>
       <c r="Z30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>211014.83333333337</v>
+        <v>213125</v>
       </c>
       <c r="AA30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>220606.41666666672</v>
+        <v>222812.5</v>
       </c>
       <c r="AB30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>230198.00000000006</v>
+        <v>232500</v>
       </c>
       <c r="AC30" s="150">
         <f t="shared" ref="AC30" ca="1" si="214">IF(AC40,AC40,AB30+AC18)</f>
-        <v>239789.5833333334</v>
+        <v>242187.5</v>
       </c>
       <c r="AD30" s="150">
         <f t="shared" ref="AD30" ca="1" si="215">IF(AD40,AD40,AC30+AD18)</f>
-        <v>249381.16666666674</v>
+        <v>251875</v>
       </c>
       <c r="AE30" s="150">
         <f t="shared" ref="AE30" ca="1" si="216">IF(AE40,AE40,AD30+AE18)</f>
-        <v>258972.75000000009</v>
+        <v>261562.5</v>
       </c>
       <c r="AF30" s="150">
         <f t="shared" ref="AF30" ca="1" si="217">IF(AF40,AF40,AE30+AF18)</f>
-        <v>268564.33333333343</v>
+        <v>271250</v>
       </c>
       <c r="AG30" s="150">
         <f t="shared" ref="AG30" ca="1" si="218">IF(AG40,AG40,AF30+AG18)</f>
-        <v>278155.91666666674</v>
+        <v>280937.5</v>
       </c>
       <c r="AH30" s="150">
         <f t="shared" ref="AH30" ca="1" si="219">IF(AH40,AH40,AG30+AH18)</f>
-        <v>287747.50000000006</v>
+        <v>290625</v>
       </c>
       <c r="AI30" s="150">
         <f t="shared" ref="AI30" ca="1" si="220">IF(AI40,AI40,AH30+AI18)</f>
-        <v>297339.08333333337</v>
+        <v>300312.5</v>
       </c>
       <c r="AJ30" s="150">
         <f t="shared" ref="AJ30" ca="1" si="221">IF(AJ40,AJ40,AI30+AJ18)</f>
-        <v>306930.66666666669</v>
+        <v>310000</v>
       </c>
       <c r="AK30" s="150">
         <f t="shared" ref="AK30" ca="1" si="222">IF(AK40,AK40,AJ30+AK18)</f>
-        <v>316522.25</v>
+        <v>319687.5</v>
       </c>
       <c r="AL30" s="150">
         <f t="shared" ref="AL30" ca="1" si="223">IF(AL40,AL40,AK30+AL18)</f>
-        <v>326113.83333333331</v>
+        <v>329375</v>
       </c>
       <c r="AM30" s="150">
         <f t="shared" ref="AM30" ca="1" si="224">IF(AM40,AM40,AL30+AM18)</f>
-        <v>335705.41666666663</v>
+        <v>339062.5</v>
       </c>
       <c r="AN30" s="150">
         <f t="shared" ref="AN30" ca="1" si="225">IF(AN40,AN40,AM30+AN18)</f>
-        <v>345296.99999999994</v>
+        <v>348750</v>
       </c>
       <c r="AO30" s="150">
         <f t="shared" ref="AO30" ca="1" si="226">IF(AO40,AO40,AN30+AO18)</f>
-        <v>354888.58333333326</v>
+        <v>358437.5</v>
       </c>
       <c r="AP30" s="150">
         <f t="shared" ref="AP30" ca="1" si="227">IF(AP40,AP40,AO30+AP18)</f>
-        <v>364480.16666666657</v>
+        <v>368125</v>
       </c>
       <c r="AQ30" s="150">
         <f t="shared" ref="AQ30" ca="1" si="228">IF(AQ40,AQ40,AP30+AQ18)</f>
-        <v>374071.74999999988</v>
+        <v>377812.5</v>
       </c>
       <c r="AR30" s="150">
         <f t="shared" ref="AR30" ca="1" si="229">IF(AR40,AR40,AQ30+AR18)</f>
-        <v>383663.3333333332</v>
+        <v>387500</v>
       </c>
       <c r="AS30" s="150">
         <f t="shared" ref="AS30" ca="1" si="230">IF(AS40,AS40,AR30+AS18)</f>
-        <v>393254.91666666651</v>
+        <v>397187.5</v>
       </c>
       <c r="AT30" s="150">
         <f t="shared" ref="AT30" ca="1" si="231">IF(AT40,AT40,AS30+AT18)</f>
-        <v>402846.49999999983</v>
+        <v>406875</v>
       </c>
       <c r="AU30" s="150">
         <f t="shared" ref="AU30" ca="1" si="232">IF(AU40,AU40,AT30+AU18)</f>
-        <v>412438.08333333314</v>
+        <v>416562.5</v>
       </c>
       <c r="AV30" s="150">
         <f t="shared" ref="AV30" ca="1" si="233">IF(AV40,AV40,AU30+AV18)</f>
-        <v>422029.66666666645</v>
+        <v>426250</v>
       </c>
       <c r="AW30" s="150">
         <f t="shared" ref="AW30" ca="1" si="234">IF(AW40,AW40,AV30+AW18)</f>
-        <v>431621.24999999977</v>
+        <v>435937.5</v>
       </c>
       <c r="AX30" s="150">
         <f t="shared" ref="AX30" ca="1" si="235">IF(AX40,AX40,AW30+AX18)</f>
-        <v>441212.83333333308</v>
+        <v>445625</v>
       </c>
       <c r="AY30" s="150">
         <f t="shared" ref="AY30" ca="1" si="236">IF(AY40,AY40,AX30+AY18)</f>
-        <v>450804.4166666664</v>
+        <v>455312.5</v>
       </c>
       <c r="AZ30" s="150">
         <f t="shared" ref="AZ30" ca="1" si="237">IF(AZ40,AZ40,AY30+AZ18)</f>
@@ -36196,195 +36194,195 @@
       </c>
       <c r="Q32" s="158">
         <f>P32+LOOKUP(Q$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(Q$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>92336.205000000031</v>
+        <v>92549.288550000027</v>
       </c>
       <c r="R32" s="158">
         <f>Q32+LOOKUP(R$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(R$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>99438.990000000034</v>
+        <v>99865.157100000026</v>
       </c>
       <c r="S32" s="158">
         <f>R32+LOOKUP(S$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(S$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>106541.77500000004</v>
+        <v>107181.02565000003</v>
       </c>
       <c r="T32" s="158">
         <f>S32+LOOKUP(T$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(T$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>113644.56000000004</v>
+        <v>114496.89420000002</v>
       </c>
       <c r="U32" s="158">
         <f>T32+LOOKUP(U$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(U$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>120747.34500000004</v>
+        <v>121812.76275000002</v>
       </c>
       <c r="V32" s="158">
         <f>U32+LOOKUP(V$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(V$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>127850.13000000005</v>
+        <v>129128.63130000002</v>
       </c>
       <c r="W32" s="158">
         <f>V32+LOOKUP(W$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(W$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>134952.91500000004</v>
+        <v>136444.49985000002</v>
       </c>
       <c r="X32" s="158">
         <f>W32+LOOKUP(X$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(X$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>142055.70000000004</v>
+        <v>143760.36840000004</v>
       </c>
       <c r="Y32" s="158">
         <f>X32+LOOKUP(Y$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(Y$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>149158.48500000004</v>
+        <v>151076.23695000005</v>
       </c>
       <c r="Z32" s="158">
         <f>Y32+LOOKUP(Z$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(Z$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>156261.27000000005</v>
+        <v>158392.10550000006</v>
       </c>
       <c r="AA32" s="158">
         <f>Z32+LOOKUP(AA$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AA$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>163364.05500000005</v>
+        <v>165707.97405000008</v>
       </c>
       <c r="AB32" s="158">
         <f>AA32+LOOKUP(AB$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AB$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>170466.84000000005</v>
+        <v>173023.84260000009</v>
       </c>
       <c r="AC32" s="158">
         <f>AB32+LOOKUP(AC$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AC$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>177569.62500000006</v>
+        <v>180559.18720650009</v>
       </c>
       <c r="AD32" s="158">
         <f>AC32+LOOKUP(AD$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AD$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>184672.41000000006</v>
+        <v>188094.5318130001</v>
       </c>
       <c r="AE32" s="158">
         <f>AD32+LOOKUP(AE$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AE$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>191775.19500000007</v>
+        <v>195629.8764195001</v>
       </c>
       <c r="AF32" s="158">
         <f>AE32+LOOKUP(AF$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AF$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>198877.98000000007</v>
+        <v>203165.2210260001</v>
       </c>
       <c r="AG32" s="158">
         <f>AF32+LOOKUP(AG$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AG$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>205980.76500000007</v>
+        <v>210700.5656325001</v>
       </c>
       <c r="AH32" s="158">
         <f>AG32+LOOKUP(AH$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AH$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>213083.55000000008</v>
+        <v>218235.91023900011</v>
       </c>
       <c r="AI32" s="158">
         <f>AH32+LOOKUP(AI$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AI$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>220186.33500000008</v>
+        <v>225771.25484550011</v>
       </c>
       <c r="AJ32" s="158">
         <f>AI32+LOOKUP(AJ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AJ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>227289.12000000008</v>
+        <v>233306.59945200011</v>
       </c>
       <c r="AK32" s="158">
         <f>AJ32+LOOKUP(AK$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AK$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>234391.90500000009</v>
+        <v>240841.94405850011</v>
       </c>
       <c r="AL32" s="158">
         <f>AK32+LOOKUP(AL$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AL$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>241494.69000000009</v>
+        <v>248377.28866500012</v>
       </c>
       <c r="AM32" s="158">
         <f>AL32+LOOKUP(AM$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AM$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>248597.47500000009</v>
+        <v>255912.63327150012</v>
       </c>
       <c r="AN32" s="158">
         <f>AM32+LOOKUP(AN$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AN$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>255700.2600000001</v>
+        <v>263447.97787800012</v>
       </c>
       <c r="AO32" s="158">
         <f>AN32+LOOKUP(AO$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AO$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>262803.0450000001</v>
+        <v>271209.38282269513</v>
       </c>
       <c r="AP32" s="158">
         <f>AO32+LOOKUP(AP$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AP$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>269905.83000000007</v>
+        <v>278970.78776739014</v>
       </c>
       <c r="AQ32" s="158">
         <f>AP32+LOOKUP(AQ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AQ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>277008.61500000005</v>
+        <v>286732.19271208515</v>
       </c>
       <c r="AR32" s="158">
         <f>AQ32+LOOKUP(AR$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AR$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>284111.40000000002</v>
+        <v>294493.59765678016</v>
       </c>
       <c r="AS32" s="158">
         <f>AR32+LOOKUP(AS$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AS$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>291214.185</v>
+        <v>302255.00260147516</v>
       </c>
       <c r="AT32" s="158">
         <f>AS32+LOOKUP(AT$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AT$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>298316.96999999997</v>
+        <v>310016.40754617017</v>
       </c>
       <c r="AU32" s="158">
         <f>AT32+LOOKUP(AU$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AU$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>305419.75499999995</v>
+        <v>317777.81249086518</v>
       </c>
       <c r="AV32" s="158">
         <f>AU32+LOOKUP(AV$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AV$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>312522.53999999992</v>
+        <v>325539.21743556019</v>
       </c>
       <c r="AW32" s="158">
         <f>AV32+LOOKUP(AW$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AW$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>319625.3249999999</v>
+        <v>333300.6223802552</v>
       </c>
       <c r="AX32" s="158">
         <f>AW32+LOOKUP(AX$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AX$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>326728.10999999987</v>
+        <v>341062.02732495021</v>
       </c>
       <c r="AY32" s="158">
         <f>AX32+LOOKUP(AY$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AY$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>333830.89499999984</v>
+        <v>348823.43226964521</v>
       </c>
       <c r="AZ32" s="158">
         <f>AY32+LOOKUP(AZ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(AZ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BA32" s="158">
         <f>AZ32+LOOKUP(BA$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BA$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BB32" s="158">
         <f>BA32+LOOKUP(BB$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BB$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BC32" s="158">
         <f>BB32+LOOKUP(BC$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BC$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BD32" s="158">
         <f>BC32+LOOKUP(BD$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BD$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BE32" s="158">
         <f>BD32+LOOKUP(BE$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BE$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BF32" s="158">
         <f>BE32+LOOKUP(BF$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BF$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BG32" s="158">
         <f>BF32+LOOKUP(BG$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BG$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BH32" s="158">
         <f>BG32+LOOKUP(BH$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BH$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BI32" s="158">
         <f>BH32+LOOKUP(BI$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BI$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BJ32" s="158">
         <f>BI32+LOOKUP(BJ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BJ$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BK32" s="158">
         <f>BJ32+LOOKUP(BK$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BK$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BL32" s="158">
         <f>BK32+LOOKUP(BL$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$40:$BO$40)+LOOKUP(BL$5,'Cost Planning'!$H$8:$BO$8,'Cost Planning'!$H$41:$BO$41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="BN32" s="21"/>
       <c r="BO32" s="21"/>
@@ -37417,7 +37415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B37" s="298" t="s">
         <v>65</v>
       </c>
@@ -37476,195 +37474,195 @@
       </c>
       <c r="Q37" s="158">
         <f t="shared" si="250"/>
-        <v>92336.205000000031</v>
+        <v>92549.288550000027</v>
       </c>
       <c r="R37" s="158">
         <f t="shared" si="250"/>
-        <v>99438.990000000034</v>
+        <v>99865.157100000026</v>
       </c>
       <c r="S37" s="158">
         <f t="shared" si="250"/>
-        <v>106541.77500000004</v>
+        <v>107181.02565000003</v>
       </c>
       <c r="T37" s="158">
         <f t="shared" si="250"/>
-        <v>113644.56000000004</v>
+        <v>114496.89420000002</v>
       </c>
       <c r="U37" s="158">
         <f t="shared" si="250"/>
-        <v>120747.34500000004</v>
+        <v>121812.76275000002</v>
       </c>
       <c r="V37" s="158">
         <f t="shared" si="250"/>
-        <v>127850.13000000005</v>
+        <v>129128.63130000002</v>
       </c>
       <c r="W37" s="158">
         <f t="shared" si="250"/>
-        <v>134952.91500000004</v>
+        <v>136444.49985000002</v>
       </c>
       <c r="X37" s="158">
         <f t="shared" si="250"/>
-        <v>142055.70000000004</v>
+        <v>143760.36840000004</v>
       </c>
       <c r="Y37" s="158">
         <f t="shared" si="250"/>
-        <v>149158.48500000004</v>
+        <v>151076.23695000005</v>
       </c>
       <c r="Z37" s="158">
         <f t="shared" si="250"/>
-        <v>156261.27000000005</v>
+        <v>158392.10550000006</v>
       </c>
       <c r="AA37" s="158">
         <f t="shared" si="250"/>
-        <v>163364.05500000005</v>
+        <v>165707.97405000008</v>
       </c>
       <c r="AB37" s="158">
         <f t="shared" si="250"/>
-        <v>170466.84000000005</v>
+        <v>173023.84260000009</v>
       </c>
       <c r="AC37" s="158">
         <f t="shared" ref="AC37:BL37" si="251">SUM(AC32:AC36)</f>
-        <v>177569.62500000006</v>
+        <v>180559.18720650009</v>
       </c>
       <c r="AD37" s="158">
         <f t="shared" si="251"/>
-        <v>184672.41000000006</v>
+        <v>188094.5318130001</v>
       </c>
       <c r="AE37" s="158">
         <f t="shared" si="251"/>
-        <v>191775.19500000007</v>
+        <v>195629.8764195001</v>
       </c>
       <c r="AF37" s="158">
         <f t="shared" si="251"/>
-        <v>198877.98000000007</v>
+        <v>203165.2210260001</v>
       </c>
       <c r="AG37" s="158">
         <f t="shared" si="251"/>
-        <v>205980.76500000007</v>
+        <v>210700.5656325001</v>
       </c>
       <c r="AH37" s="158">
         <f t="shared" si="251"/>
-        <v>213083.55000000008</v>
+        <v>218235.91023900011</v>
       </c>
       <c r="AI37" s="158">
         <f t="shared" si="251"/>
-        <v>220186.33500000008</v>
+        <v>225771.25484550011</v>
       </c>
       <c r="AJ37" s="158">
         <f t="shared" si="251"/>
-        <v>227289.12000000008</v>
+        <v>233306.59945200011</v>
       </c>
       <c r="AK37" s="158">
         <f t="shared" si="251"/>
-        <v>234391.90500000009</v>
+        <v>240841.94405850011</v>
       </c>
       <c r="AL37" s="158">
         <f t="shared" si="251"/>
-        <v>241494.69000000009</v>
+        <v>248377.28866500012</v>
       </c>
       <c r="AM37" s="158">
         <f t="shared" si="251"/>
-        <v>248597.47500000009</v>
+        <v>255912.63327150012</v>
       </c>
       <c r="AN37" s="158">
         <f t="shared" si="251"/>
-        <v>255700.2600000001</v>
+        <v>263447.97787800012</v>
       </c>
       <c r="AO37" s="158">
         <f t="shared" si="251"/>
-        <v>262803.0450000001</v>
+        <v>271209.38282269513</v>
       </c>
       <c r="AP37" s="158">
         <f t="shared" si="251"/>
-        <v>269905.83000000007</v>
+        <v>278970.78776739014</v>
       </c>
       <c r="AQ37" s="158">
         <f t="shared" si="251"/>
-        <v>277008.61500000005</v>
+        <v>286732.19271208515</v>
       </c>
       <c r="AR37" s="158">
         <f t="shared" si="251"/>
-        <v>284111.40000000002</v>
+        <v>294493.59765678016</v>
       </c>
       <c r="AS37" s="158">
         <f t="shared" si="251"/>
-        <v>291214.185</v>
+        <v>302255.00260147516</v>
       </c>
       <c r="AT37" s="158">
         <f t="shared" si="251"/>
-        <v>298316.96999999997</v>
+        <v>310016.40754617017</v>
       </c>
       <c r="AU37" s="158">
         <f t="shared" si="251"/>
-        <v>305419.75499999995</v>
+        <v>317777.81249086518</v>
       </c>
       <c r="AV37" s="158">
         <f t="shared" si="251"/>
-        <v>312522.53999999992</v>
+        <v>325539.21743556019</v>
       </c>
       <c r="AW37" s="158">
         <f t="shared" si="251"/>
-        <v>319625.3249999999</v>
+        <v>333300.6223802552</v>
       </c>
       <c r="AX37" s="158">
         <f t="shared" si="251"/>
-        <v>326728.10999999987</v>
+        <v>341062.02732495021</v>
       </c>
       <c r="AY37" s="158">
         <f t="shared" si="251"/>
-        <v>333830.89499999984</v>
+        <v>348823.43226964521</v>
       </c>
       <c r="AZ37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BA37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BB37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BC37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BD37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BE37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BF37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BG37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BH37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BI37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BJ37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BK37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="BL37" s="158">
         <f t="shared" si="251"/>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
     </row>
     <row r="38" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
@@ -37678,243 +37676,243 @@
       </c>
       <c r="E38" s="159">
         <f ca="1">E30-E32-E33-E34-E35-E36</f>
-        <v>2488.7983333333323</v>
+        <v>2584.7150000000001</v>
       </c>
       <c r="F38" s="159">
         <f t="shared" ref="F38:Z38" ca="1" si="252">F30-F32-F33-F34-F35-F36</f>
-        <v>4977.5966666666645</v>
+        <v>5169.43</v>
       </c>
       <c r="G38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>7466.3949999999968</v>
+        <v>7754.1450000000004</v>
       </c>
       <c r="H38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>9955.1933333333291</v>
+        <v>10338.86</v>
       </c>
       <c r="I38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>12443.991666666654</v>
+        <v>12923.574999999997</v>
       </c>
       <c r="J38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>14932.789999999979</v>
+        <v>15508.289999999994</v>
       </c>
       <c r="K38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>17421.588333333304</v>
+        <v>18093.00499999999</v>
       </c>
       <c r="L38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>19910.386666666629</v>
+        <v>20677.719999999987</v>
       </c>
       <c r="M38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>22399.184999999954</v>
+        <v>23262.434999999983</v>
       </c>
       <c r="N38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>24887.983333333279</v>
+        <v>25847.14999999998</v>
       </c>
       <c r="O38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>27376.781666666604</v>
+        <v>28431.864999999976</v>
       </c>
       <c r="P38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>29865.579999999929</v>
+        <v>31016.579999999973</v>
       </c>
       <c r="Q38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>32354.378333333254</v>
+        <v>33388.211449999973</v>
       </c>
       <c r="R38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>34843.176666666594</v>
+        <v>35759.842899999974</v>
       </c>
       <c r="S38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>37331.974999999933</v>
+        <v>38131.474349999975</v>
       </c>
       <c r="T38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>39820.773333333273</v>
+        <v>40503.105799999976</v>
       </c>
       <c r="U38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>42309.571666666612</v>
+        <v>42874.737249999976</v>
       </c>
       <c r="V38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>44798.369999999952</v>
+        <v>45246.368699999977</v>
       </c>
       <c r="W38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>47287.168333333306</v>
+        <v>47618.000149999978</v>
       </c>
       <c r="X38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>49775.966666666645</v>
+        <v>49989.631599999964</v>
       </c>
       <c r="Y38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>52264.764999999985</v>
+        <v>52361.26304999995</v>
       </c>
       <c r="Z38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>54753.563333333324</v>
+        <v>54732.894499999937</v>
       </c>
       <c r="AA38" s="159">
         <f ca="1">AA30-AA32-AA33-AA34-AA35-AA36</f>
-        <v>57242.361666666664</v>
+        <v>57104.525949999923</v>
       </c>
       <c r="AB38" s="159">
         <f ca="1">AB30-AB32-AB33-AB34-AB35-AB36</f>
-        <v>59731.16</v>
+        <v>59476.157399999909</v>
       </c>
       <c r="AC38" s="159">
         <f t="shared" ref="AC38:BL38" ca="1" si="253">AC30-AC32-AC33-AC34-AC35-AC36</f>
-        <v>62219.958333333343</v>
+        <v>61628.312793499907</v>
       </c>
       <c r="AD38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>64708.756666666683</v>
+        <v>63780.468186999904</v>
       </c>
       <c r="AE38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>67197.555000000022</v>
+        <v>65932.623580499901</v>
       </c>
       <c r="AF38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>69686.353333333362</v>
+        <v>68084.778973999899</v>
       </c>
       <c r="AG38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>72175.151666666672</v>
+        <v>70236.934367499896</v>
       </c>
       <c r="AH38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>74663.949999999983</v>
+        <v>72389.089760999894</v>
       </c>
       <c r="AI38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>77152.748333333293</v>
+        <v>74541.245154499891</v>
       </c>
       <c r="AJ38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>79641.546666666603</v>
+        <v>76693.400547999889</v>
       </c>
       <c r="AK38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>82130.344999999914</v>
+        <v>78845.555941499886</v>
       </c>
       <c r="AL38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>84619.143333333224</v>
+        <v>80997.711334999884</v>
       </c>
       <c r="AM38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>87107.941666666535</v>
+        <v>83149.866728499881</v>
       </c>
       <c r="AN38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>89596.739999999845</v>
+        <v>85302.022121999878</v>
       </c>
       <c r="AO38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>92085.538333333156</v>
+        <v>87228.11717730487</v>
       </c>
       <c r="AP38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>94574.336666666495</v>
+        <v>89154.212232609862</v>
       </c>
       <c r="AQ38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>97063.134999999835</v>
+        <v>91080.307287914853</v>
       </c>
       <c r="AR38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>99551.933333333174</v>
+        <v>93006.402343219845</v>
       </c>
       <c r="AS38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>102040.73166666651</v>
+        <v>94932.497398524836</v>
       </c>
       <c r="AT38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>104529.52999999985</v>
+        <v>96858.592453829828</v>
       </c>
       <c r="AU38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>107018.32833333319</v>
+        <v>98784.687509134819</v>
       </c>
       <c r="AV38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>109507.12666666653</v>
+        <v>100710.78256443981</v>
       </c>
       <c r="AW38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>111995.92499999987</v>
+        <v>102636.8776197448</v>
       </c>
       <c r="AX38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>114484.72333333321</v>
+        <v>104562.97267504979</v>
       </c>
       <c r="AY38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>116973.52166666655</v>
+        <v>106489.06773035479</v>
       </c>
       <c r="AZ38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BA38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BB38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BC38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BD38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BE38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BF38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BG38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BH38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BI38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BJ38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BK38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
       <c r="BL38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>120500.47000000018</v>
+        <v>104849.31278565977</v>
       </c>
     </row>
     <row r="39" spans="2:77" x14ac:dyDescent="0.3">
@@ -38641,191 +38639,191 @@
       <c r="D44" s="160"/>
       <c r="E44" s="160">
         <f t="shared" ref="E44:Z44" ca="1" si="294">E43-E30</f>
-        <v>-9591.5833333333321</v>
+        <v>-9687.5</v>
       </c>
       <c r="F44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-19183.166666666664</v>
+        <v>-19375</v>
       </c>
       <c r="G44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-28774.749999999996</v>
+        <v>-29062.5</v>
       </c>
       <c r="H44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-38366.333333333328</v>
+        <v>-38750</v>
       </c>
       <c r="I44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-47957.916666666657</v>
+        <v>-48437.5</v>
       </c>
       <c r="J44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-57549.499999999985</v>
+        <v>-58125</v>
       </c>
       <c r="K44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-67141.083333333314</v>
+        <v>-67812.5</v>
       </c>
       <c r="L44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-76732.666666666642</v>
+        <v>-77500</v>
       </c>
       <c r="M44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-86324.249999999971</v>
+        <v>-87187.5</v>
       </c>
       <c r="N44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-95915.833333333299</v>
+        <v>-96875</v>
       </c>
       <c r="O44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-105507.41666666663</v>
+        <v>-106562.5</v>
       </c>
       <c r="P44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-115098.99999999996</v>
+        <v>-116250</v>
       </c>
       <c r="Q44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-124690.58333333328</v>
+        <v>-125937.5</v>
       </c>
       <c r="R44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-134282.16666666663</v>
+        <v>-135625</v>
       </c>
       <c r="S44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-143873.74999999997</v>
+        <v>-145312.5</v>
       </c>
       <c r="T44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-153465.33333333331</v>
+        <v>-155000</v>
       </c>
       <c r="U44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-163056.91666666666</v>
+        <v>-164687.5</v>
       </c>
       <c r="V44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-172648.5</v>
+        <v>-174375</v>
       </c>
       <c r="W44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-182240.08333333334</v>
+        <v>-184062.5</v>
       </c>
       <c r="X44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-191831.66666666669</v>
+        <v>-193750</v>
       </c>
       <c r="Y44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-201423.25000000003</v>
+        <v>-203437.5</v>
       </c>
       <c r="Z44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-211014.83333333337</v>
+        <v>-213125</v>
       </c>
       <c r="AA44" s="160">
         <f ca="1">AA43-AA30</f>
-        <v>-220606.41666666672</v>
+        <v>-222812.5</v>
       </c>
       <c r="AB44" s="160">
         <f ca="1">AB43-AB30</f>
-        <v>-230198.00000000006</v>
+        <v>-232500</v>
       </c>
       <c r="AC44" s="160">
         <f t="shared" ref="AC44:BL44" ca="1" si="295">AC43-AC30</f>
-        <v>-239789.5833333334</v>
+        <v>-242187.5</v>
       </c>
       <c r="AD44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-249381.16666666674</v>
+        <v>-251875</v>
       </c>
       <c r="AE44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-258972.75000000009</v>
+        <v>-261562.5</v>
       </c>
       <c r="AF44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-268564.33333333343</v>
+        <v>-271250</v>
       </c>
       <c r="AG44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-278155.91666666674</v>
+        <v>-280937.5</v>
       </c>
       <c r="AH44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-287747.50000000006</v>
+        <v>-290625</v>
       </c>
       <c r="AI44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-297339.08333333337</v>
+        <v>-300312.5</v>
       </c>
       <c r="AJ44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-306930.66666666669</v>
+        <v>-310000</v>
       </c>
       <c r="AK44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-316522.25</v>
+        <v>-319687.5</v>
       </c>
       <c r="AL44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-326113.83333333331</v>
+        <v>-329375</v>
       </c>
       <c r="AM44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-335705.41666666663</v>
+        <v>-339062.5</v>
       </c>
       <c r="AN44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-345296.99999999994</v>
+        <v>-348750</v>
       </c>
       <c r="AO44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-354888.58333333326</v>
+        <v>-358437.5</v>
       </c>
       <c r="AP44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-364480.16666666657</v>
+        <v>-368125</v>
       </c>
       <c r="AQ44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-374071.74999999988</v>
+        <v>-377812.5</v>
       </c>
       <c r="AR44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-383663.3333333332</v>
+        <v>-387500</v>
       </c>
       <c r="AS44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-393254.91666666651</v>
+        <v>-397187.5</v>
       </c>
       <c r="AT44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-402846.49999999983</v>
+        <v>-406875</v>
       </c>
       <c r="AU44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-412438.08333333314</v>
+        <v>-416562.5</v>
       </c>
       <c r="AV44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-422029.66666666645</v>
+        <v>-426250</v>
       </c>
       <c r="AW44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-431621.24999999977</v>
+        <v>-435937.5</v>
       </c>
       <c r="AX44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-441212.83333333308</v>
+        <v>-445625</v>
       </c>
       <c r="AY44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-450804.4166666664</v>
+        <v>-455312.5</v>
       </c>
       <c r="AZ44" s="160">
         <f t="shared" ca="1" si="295"/>
@@ -40536,7 +40534,7 @@
       </c>
       <c r="E8" s="209">
         <f>SUM('Cost Planning'!F40:BO41)</f>
-        <v>340933.67999999982</v>
+        <v>356584.83721434022</v>
       </c>
       <c r="F8" s="209">
         <f>SUM('Cost Planning'!F9:BO9)</f>
@@ -40560,19 +40558,19 @@
       </c>
       <c r="K8" s="209">
         <f>SUM(E8,G8,H8,I8,J8)</f>
-        <v>344499.5299999998</v>
+        <v>360150.6872143402</v>
       </c>
       <c r="L8" s="209">
         <f>D8-K8</f>
-        <v>120500.4700000002</v>
+        <v>104849.3127856598</v>
       </c>
       <c r="M8" s="210">
         <f>IF(D8=0,0,(D8-E8-H8-I8-G8-J8)/D8)</f>
-        <v>0.25914079569892512</v>
+        <v>0.22548239308744036</v>
       </c>
       <c r="N8" s="210">
         <f>IF(D8=0,0,(D8-E8/UTILIZACION-G8/UTILIZACION-H8/UTILIZACION-I8-J8)/D8)</f>
-        <v>0.20337719967626361</v>
+        <v>0.16718536891122623</v>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="22"/>
@@ -40588,7 +40586,7 @@
       </c>
       <c r="E9" s="211">
         <f t="shared" ref="E9:L9" si="0">IF(E8=0,1,(E8-E7)/E8)</f>
-        <v>-4.5906758170680628E-2</v>
+        <v>-7.8120534355124018E-9</v>
       </c>
       <c r="F9" s="211">
         <f t="shared" si="0"/>
@@ -40612,15 +40610,15 @@
       </c>
       <c r="K9" s="211">
         <f t="shared" si="0"/>
-        <v>-4.5431585929885644E-2</v>
+        <v>-7.7347063368341113E-9</v>
       </c>
       <c r="L9" s="211">
         <f t="shared" si="0"/>
-        <v>0.12988463862423258</v>
+        <v>2.6568221847162273E-8</v>
       </c>
       <c r="M9" s="212">
         <f>M8-M7</f>
-        <v>3.3658408602150997E-2</v>
+        <v>5.9906662408515388E-9</v>
       </c>
       <c r="N9" s="293"/>
       <c r="O9" s="24"/>
@@ -40650,15 +40648,15 @@
       <c r="C11" s="307"/>
       <c r="D11" s="202">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$18:$BL$18)+'Project Infor'!C45</f>
-        <v>57549.499999999985</v>
+        <v>0</v>
       </c>
       <c r="E11" s="202">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$20:$BL$20)+'Project Infor'!C47</f>
-        <v>42616.710000000006</v>
+        <v>0</v>
       </c>
       <c r="F11" s="202">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$19:$BL$19)+'Project Infor'!C46</f>
-        <v>1782</v>
+        <v>0</v>
       </c>
       <c r="G11" s="202">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$21:$BL$21)</f>
@@ -40678,19 +40676,19 @@
       </c>
       <c r="K11" s="202">
         <f>SUM(E11,G11,H11,I11,J11)</f>
-        <v>42616.710000000006</v>
+        <v>0</v>
       </c>
       <c r="L11" s="202">
         <f>D11-K11</f>
-        <v>14932.789999999979</v>
+        <v>0</v>
       </c>
       <c r="M11" s="203">
         <f>IF(D11=0,0,(D11-E11-H11-I11-G11-J11)/D11)</f>
-        <v>0.25947731952493042</v>
+        <v>0</v>
       </c>
       <c r="N11" s="201">
         <f>IF(D11=0,0,(D11-E11/UTILIZACION-G11/UTILIZACION-H11/UTILIZACION-I11-J11)/D11)</f>
-        <v>0.20373905325261343</v>
+        <v>0</v>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="22"/>
@@ -40701,16 +40699,16 @@
       </c>
       <c r="C12" s="305"/>
       <c r="D12" s="165">
-        <f>IF(D11=0,1,(D11/D8))</f>
-        <v>0.12376236559139782</v>
+        <f>IF(D8=0,0,D11/D8)</f>
+        <v>0</v>
       </c>
       <c r="E12" s="165">
-        <f>IF(E11=0,1,(E11/E8))</f>
-        <v>0.12500000000000008</v>
+        <f>IF(E8=0,0,E11/E8)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="165">
-        <f>IF(F11=0,1,(F11/F8))</f>
-        <v>0.125</v>
+        <f>IF(F8=0,0,F11/F8)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="165"/>
       <c r="H12" s="165"/>
@@ -43021,6 +43019,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005104B4C06FD53E4DA82687A05841D03F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f48deddc6bffdc45fb3ed0ec71e33c6c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7dc5af80-ab8f-4cff-b7cb-3463b3238b39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a8808579f8fa9f9643be1385777e037d" ns2:_="">
     <xsd:import namespace="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
@@ -43194,22 +43207,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4453D5CC-2F3C-48AA-8382-954EB2322467}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794A36B1-E557-480A-80A5-281FC452AC8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F36A1B76-9E34-462B-9C68-1BC8027D2211}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43227,23 +43242,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794A36B1-E557-480A-80A5-281FC452AC8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4453D5CC-2F3C-48AA-8382-954EB2322467}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{040b5de6-6e2e-46f2-bca1-507eb809bbf7}" enabled="1" method="Privileged" siteId="{56d7daaa-b378-45b3-aa11-af9402b401b9}" contentBits="0" removed="0"/>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.36-e08\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-e08-review\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF1E34C-BE92-4D2C-88FB-E9FF413B65EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14182B84-3424-4F58-AD69-AF528E0228C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="300">
   <si>
     <t>CORE (COst REport) - AT</t>
   </si>
@@ -617,9 +617,6 @@
     <t>COSTE TOTAL GASTOS BASELINE</t>
   </si>
   <si>
-    <t>(!) El coste de GASTOS planificado es mayor que el de la BASELINE</t>
-  </si>
-  <si>
     <t>TIPO GASTO</t>
   </si>
   <si>
@@ -642,9 +639,6 @@
   </si>
   <si>
     <t xml:space="preserve">COSTE TOTAL COMPRAS BASELINE </t>
-  </si>
-  <si>
-    <t>(!) El coste de COMPRAS planificado es mayor que el de la BASELINE</t>
   </si>
   <si>
     <t>PROVEEDOR</t>
@@ -1078,6 +1072,9 @@
     <t>AMS</t>
   </si>
   <si>
+    <t>Compania: Connectis-ICT | Unidad: ICT | Portfolio: Sin producto | Subpractice: Norte | Origen: EV1AP0</t>
+  </si>
+  <si>
     <t>CUST-CE-JCYL-TEST</t>
   </si>
   <si>
@@ -1126,7 +1123,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>Generado por RPA: 2026-05-11 10:20:45 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual.</t>
+    <t>Generado por RPA: 2026-05-11 10:50:00 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual.</t>
   </si>
 </sst>
 </file>
@@ -7728,7 +7725,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="289" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D10" s="290"/>
       <c r="H10" s="24"/>
@@ -7746,7 +7743,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="318" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D11" s="318"/>
       <c r="E11" s="318"/>
@@ -7767,7 +7764,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="315" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D12" s="315"/>
       <c r="H12" s="24"/>
@@ -7784,7 +7781,9 @@
       <c r="B13" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="316"/>
+      <c r="C13" s="316" t="s">
+        <v>282</v>
+      </c>
       <c r="D13" s="317"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7836,10 +7835,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
@@ -7876,7 +7875,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="24"/>
@@ -7897,7 +7896,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="177" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="70"/>
@@ -7956,10 +7955,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>288</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>289</v>
       </c>
       <c r="E22" s="70"/>
       <c r="F22" s="181"/>
@@ -7979,10 +7978,10 @@
         <v>17</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>290</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>291</v>
       </c>
       <c r="E23" s="70"/>
       <c r="F23" s="181"/>
@@ -8002,10 +8001,10 @@
         <v>18</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D24" s="178" t="s">
         <v>292</v>
-      </c>
-      <c r="D24" s="178" t="s">
-        <v>293</v>
       </c>
       <c r="E24" s="70"/>
       <c r="F24" s="181"/>
@@ -8708,7 +8707,7 @@
     </row>
     <row r="61" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C61" s="24"/>
       <c r="D61" s="24"/>
@@ -8727,7 +8726,7 @@
     </row>
     <row r="62" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C62" s="24"/>
       <c r="D62" s="24"/>
@@ -8746,12 +8745,12 @@
     </row>
     <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
@@ -8775,7 +8774,7 @@
     </row>
     <row r="66" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -8823,7 +8822,7 @@
     </row>
     <row r="70" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
@@ -8862,7 +8861,7 @@
     </row>
     <row r="75" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
@@ -9010,28 +9009,28 @@
     </row>
     <row r="4" spans="2:23" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="77" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C4" s="315" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D4" s="315"/>
       <c r="E4" s="22"/>
       <c r="F4" s="332" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G4" s="333"/>
       <c r="H4" s="228" t="s">
+        <v>239</v>
+      </c>
+      <c r="I4" s="228" t="s">
+        <v>240</v>
+      </c>
+      <c r="J4" s="228" t="s">
         <v>241</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="K4" s="332" t="s">
         <v>242</v>
-      </c>
-      <c r="J4" s="228" t="s">
-        <v>243</v>
-      </c>
-      <c r="K4" s="332" t="s">
-        <v>244</v>
       </c>
       <c r="L4" s="332"/>
       <c r="M4" s="332"/>
@@ -9039,15 +9038,15 @@
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="77" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C5" s="330" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D5" s="330"/>
       <c r="E5" s="22"/>
       <c r="F5" s="330" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G5" s="330"/>
       <c r="H5" s="230">
@@ -9057,7 +9056,7 @@
         <v>5000</v>
       </c>
       <c r="J5" s="289" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K5" s="330"/>
       <c r="L5" s="330"/>
@@ -9066,15 +9065,15 @@
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="77" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C6" s="330" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D6" s="330"/>
       <c r="E6" s="22"/>
       <c r="F6" s="330" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G6" s="330"/>
       <c r="H6" s="230">
@@ -9091,17 +9090,17 @@
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="77" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C7" s="331">
         <v>10000</v>
       </c>
       <c r="D7" s="331"/>
       <c r="E7" s="229" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F7" s="330" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G7" s="330"/>
       <c r="H7" s="230">
@@ -9120,7 +9119,7 @@
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="330" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G8" s="330"/>
       <c r="H8" s="230">
@@ -9139,7 +9138,7 @@
       <c r="D9" s="22"/>
       <c r="E9" s="56"/>
       <c r="F9" s="330" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G9" s="330"/>
       <c r="H9" s="230">
@@ -9158,7 +9157,7 @@
     </row>
     <row r="10" spans="2:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="310" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" s="310"/>
       <c r="M10" s="24"/>
@@ -9182,46 +9181,46 @@
     </row>
     <row r="12" spans="2:23" s="86" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="42" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C12" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="E12" s="42" t="s">
+      <c r="F12" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="G12" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="H12" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="I12" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="I12" s="42" t="s">
+      <c r="J12" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="J12" s="42" t="s">
+      <c r="K12" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="L12" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="K12" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="L12" s="43" t="s">
+      <c r="M12" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="N12" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="M12" s="43" t="s">
+      <c r="O12" s="43" t="s">
         <v>232</v>
-      </c>
-      <c r="N12" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="O12" s="43" t="s">
-        <v>234</v>
       </c>
       <c r="P12" s="24"/>
       <c r="Q12" s="21"/>
@@ -9234,22 +9233,22 @@
     </row>
     <row r="13" spans="2:23" s="67" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="199" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13" s="226">
         <v>44286</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F13" s="5">
         <v>3000</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H13" s="8">
         <v>0.21</v>
@@ -9259,12 +9258,12 @@
         <v>3630</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="55"/>
       <c r="M13" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -10239,7 +10238,7 @@
     </row>
     <row r="46" spans="2:23" s="89" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="327" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C46" s="327"/>
       <c r="D46" s="327"/>
@@ -10387,7 +10386,7 @@
     <row r="53" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C55" s="65"/>
       <c r="D55" s="65"/>
@@ -10534,11 +10533,11 @@
     </row>
     <row r="5" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="334" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C5" s="334"/>
       <c r="D5" s="335" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E5" s="335"/>
       <c r="F5" s="335"/>
@@ -10557,10 +10556,10 @@
     </row>
     <row r="6" spans="1:41" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="291" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C6" s="291" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D6" s="234">
         <f>'Project Infor'!$C$8</f>
@@ -10946,7 +10945,7 @@
     <row r="12" spans="1:41" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="262"/>
       <c r="C12" s="262" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D12" s="263">
         <f>SUMPRODUCT(D7:D11,$B$7:$B$11)</f>
@@ -11093,11 +11092,11 @@
     </row>
     <row r="15" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="334" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C15" s="334"/>
       <c r="D15" s="335" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E15" s="335"/>
       <c r="F15" s="335"/>
@@ -11116,10 +11115,10 @@
     </row>
     <row r="16" spans="1:41" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="291" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C16" s="291" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D16" s="234">
         <f>'Project Infor'!$C$8</f>
@@ -11462,7 +11461,7 @@
     <row r="22" spans="1:41" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="262"/>
       <c r="C22" s="262" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D22" s="263">
         <f t="shared" ref="D22:AB22" si="47">SUMPRODUCT(D17:D21,$B$17:$B$21)</f>
@@ -11609,11 +11608,11 @@
     </row>
     <row r="25" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="334" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C25" s="334"/>
       <c r="D25" s="335" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E25" s="335"/>
       <c r="F25" s="335"/>
@@ -11632,10 +11631,10 @@
     </row>
     <row r="26" spans="1:41" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="291" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C26" s="291" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D26" s="234">
         <f>'Project Infor'!$C$8</f>
@@ -11992,7 +11991,7 @@
     <row r="32" spans="1:41" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="262"/>
       <c r="C32" s="262" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D32" s="263">
         <f t="shared" ref="D32:AB32" si="73">SUMPRODUCT(D27:D31,$B$27:$B$31)</f>
@@ -12139,11 +12138,11 @@
     </row>
     <row r="35" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="334" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C35" s="334"/>
       <c r="D35" s="335" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E35" s="335"/>
       <c r="F35" s="335"/>
@@ -12162,10 +12161,10 @@
     </row>
     <row r="36" spans="1:41" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="291" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C36" s="291" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D36" s="234">
         <f>'Project Infor'!$C$8</f>
@@ -12506,7 +12505,7 @@
     <row r="42" spans="1:41" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="262"/>
       <c r="C42" s="262" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D42" s="263">
         <f t="shared" ref="D42:AB42" si="99">SUMPRODUCT(D37:D41,$B$37:$B$41)</f>
@@ -12653,11 +12652,11 @@
     </row>
     <row r="45" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="334" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C45" s="334"/>
       <c r="D45" s="335" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E45" s="335"/>
       <c r="F45" s="335"/>
@@ -12676,10 +12675,10 @@
     </row>
     <row r="46" spans="1:41" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="291" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C46" s="291" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D46" s="234">
         <f>'Project Infor'!$C$8</f>
@@ -13020,7 +13019,7 @@
     <row r="52" spans="1:41" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="262"/>
       <c r="C52" s="262" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D52" s="263">
         <f>SUMPRODUCT(D47:D51,$B$47:$B$51)</f>
@@ -13167,11 +13166,11 @@
     </row>
     <row r="55" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="334" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C55" s="334"/>
       <c r="D55" s="335" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E55" s="335"/>
       <c r="F55" s="335"/>
@@ -13190,10 +13189,10 @@
     </row>
     <row r="56" spans="1:41" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="291" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C56" s="291" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D56" s="234">
         <f>'Project Infor'!$C$8</f>
@@ -13525,7 +13524,7 @@
     <row r="62" spans="1:41" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="262"/>
       <c r="C62" s="262" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D62" s="263">
         <f>SUMPRODUCT(D57:D61,$B$57:$B$61)</f>
@@ -16028,16 +16027,16 @@
     </row>
     <row r="7" spans="2:79" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C7" t="s">
         <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F7" s="283" t="s">
         <v>91</v>
@@ -16213,16 +16212,16 @@
     </row>
     <row r="8" spans="2:79" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
         <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F8" s="284" t="s">
         <v>92</v>
@@ -16398,16 +16397,16 @@
     </row>
     <row r="9" spans="2:79" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F9" s="283" t="s">
         <v>91</v>
@@ -16583,16 +16582,16 @@
     </row>
     <row r="10" spans="2:79" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C10" t="s">
         <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F10" s="284" t="s">
         <v>92</v>
@@ -16768,16 +16767,16 @@
     </row>
     <row r="11" spans="2:79" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C11" t="s">
         <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F11" s="283" t="s">
         <v>91</v>
@@ -16953,16 +16952,16 @@
     </row>
     <row r="12" spans="2:79" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C12" t="s">
         <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F12" s="284" t="s">
         <v>92</v>
@@ -20663,8 +20662,8 @@
       </c>
       <c r="I5" s="113"/>
       <c r="J5" s="114">
-        <f>F5-SUM(F40:BO41)</f>
-        <v>2.7856598026119173E-3</v>
+        <f>ROUND(F5-SUM(F40:BO41),2)</f>
+        <v>0</v>
       </c>
       <c r="K5" s="99"/>
       <c r="L5" s="275" t="s">
@@ -21424,16 +21423,16 @@
     </row>
     <row r="10" spans="2:80" s="104" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C10" t="s">
         <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F10"/>
       <c r="G10" s="285" t="s">
@@ -21610,16 +21609,16 @@
     </row>
     <row r="11" spans="2:80" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
         <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="286" t="s">
@@ -21796,16 +21795,16 @@
     </row>
     <row r="12" spans="2:80" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C12" t="s">
         <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F12"/>
       <c r="G12" s="285" t="s">
@@ -21982,16 +21981,16 @@
     </row>
     <row r="13" spans="2:80" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
         <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F13"/>
       <c r="G13" s="286" t="s">
@@ -22168,16 +22167,16 @@
     </row>
     <row r="14" spans="2:80" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C14" t="s">
         <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F14"/>
       <c r="G14" s="285" t="s">
@@ -22354,16 +22353,16 @@
     </row>
     <row r="15" spans="2:80" s="104" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
         <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F15"/>
       <c r="G15" s="286" t="s">
@@ -25723,12 +25722,13 @@
       </c>
       <c r="I50" s="113"/>
       <c r="J50" s="114">
-        <f>F50-SUM(F61:BO61)</f>
+        <f>ROUND(F50-SUM(F61:BO61),2)</f>
         <v>0</v>
       </c>
       <c r="K50" s="99"/>
-      <c r="L50" s="296" t="s">
-        <v>142</v>
+      <c r="L50" s="296" t="str">
+        <f>IF(J50&lt;-0.005,"(!) El coste de GASTOS planificado es mayor que el de la BASELINE","")</f>
+        <v/>
       </c>
       <c r="M50" s="296"/>
       <c r="N50" s="296"/>
@@ -25757,20 +25757,20 @@
     </row>
     <row r="52" spans="2:80" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="291" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="291" t="s">
         <v>143</v>
       </c>
-      <c r="C52" s="291" t="s">
+      <c r="D52" s="291" t="s">
         <v>144</v>
-      </c>
-      <c r="D52" s="291" t="s">
-        <v>145</v>
       </c>
       <c r="E52" s="291"/>
       <c r="F52" s="101" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" s="101" t="s">
         <v>146</v>
-      </c>
-      <c r="G52" s="101" t="s">
-        <v>147</v>
       </c>
       <c r="H52" s="102">
         <f>'Project Infor'!C8</f>
@@ -26700,7 +26700,7 @@
     </row>
     <row r="61" spans="2:80" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="117" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C61" s="118"/>
       <c r="D61" s="119"/>
@@ -26950,7 +26950,7 @@
     </row>
     <row r="62" spans="2:80" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="121" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C62" s="122"/>
       <c r="D62" s="123"/>
@@ -27222,7 +27222,7 @@
       </c>
       <c r="C64" s="99"/>
       <c r="D64" s="111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E64" s="111"/>
       <c r="F64" s="278">
@@ -27235,12 +27235,13 @@
       </c>
       <c r="I64" s="276"/>
       <c r="J64" s="114">
-        <f>F64-SUM(F77:BO77)</f>
+        <f>ROUND(F64-SUM(F77:BO77),2)</f>
         <v>0</v>
       </c>
       <c r="K64" s="99"/>
-      <c r="L64" s="296" t="s">
-        <v>151</v>
+      <c r="L64" s="296" t="str">
+        <f>IF(J64&lt;-0.005,"(!) El coste de COMPRAS planificado es mayor que el de la BASELINE","")</f>
+        <v/>
       </c>
       <c r="M64" s="296"/>
       <c r="N64" s="296"/>
@@ -27269,22 +27270,22 @@
     </row>
     <row r="66" spans="2:80" s="103" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="291" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="291" t="s">
+        <v>151</v>
+      </c>
+      <c r="D66" s="291" t="s">
         <v>152</v>
       </c>
-      <c r="C66" s="291" t="s">
+      <c r="E66" s="291" t="s">
         <v>153</v>
       </c>
-      <c r="D66" s="291" t="s">
-        <v>154</v>
-      </c>
-      <c r="E66" s="291" t="s">
-        <v>155</v>
-      </c>
       <c r="F66" s="101" t="s">
+        <v>145</v>
+      </c>
+      <c r="G66" s="101" t="s">
         <v>146</v>
-      </c>
-      <c r="G66" s="101" t="s">
-        <v>147</v>
       </c>
       <c r="H66" s="102">
         <f>'Project Infor'!C8</f>
@@ -28382,7 +28383,7 @@
     </row>
     <row r="77" spans="2:80" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="138" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C77" s="139"/>
       <c r="D77" s="139"/>
@@ -28632,7 +28633,7 @@
     </row>
     <row r="78" spans="2:80" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="121" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C78" s="122"/>
       <c r="D78" s="123"/>
@@ -29097,37 +29098,37 @@
     </row>
     <row r="88" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B88" s="141" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B89" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B90" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B91" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B92" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B93" s="21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="2:67" ht="14" x14ac:dyDescent="0.3">
       <c r="B94" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95" spans="2:67" ht="14" x14ac:dyDescent="0.3">
@@ -29508,7 +29509,7 @@
       <c r="F2" s="96"/>
       <c r="G2" s="96"/>
       <c r="I2" s="294" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J2" s="294"/>
       <c r="K2" s="294"/>
@@ -29772,11 +29773,11 @@
     </row>
     <row r="5" spans="2:77" s="86" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="291" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C5" s="291"/>
       <c r="D5" s="145" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E5" s="146">
         <v>46023</v>
@@ -29986,7 +29987,7 @@
     </row>
     <row r="6" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="297" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C6" s="297"/>
       <c r="D6" s="149">
@@ -30511,7 +30512,7 @@
     </row>
     <row r="8" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="298" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C8" s="298"/>
       <c r="D8" s="151">
@@ -30773,7 +30774,7 @@
     </row>
     <row r="9" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="298" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C9" s="298"/>
       <c r="D9" s="151">
@@ -31035,7 +31036,7 @@
     </row>
     <row r="10" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="298" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C10" s="298"/>
       <c r="D10" s="151">
@@ -31297,7 +31298,7 @@
     </row>
     <row r="11" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="298" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C11" s="298"/>
       <c r="D11" s="151">
@@ -31547,7 +31548,7 @@
     </row>
     <row r="12" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="298" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C12" s="298"/>
       <c r="D12" s="151">
@@ -31795,7 +31796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="298" t="s">
         <v>65</v>
       </c>
@@ -32047,7 +32048,7 @@
     </row>
     <row r="14" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="299" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C14" s="299"/>
       <c r="D14" s="153">
@@ -32297,7 +32298,7 @@
     </row>
     <row r="15" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="299" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C15" s="299"/>
       <c r="D15" s="154">
@@ -32553,7 +32554,7 @@
     </row>
     <row r="17" spans="2:77" s="86" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="291" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C17" s="291"/>
       <c r="D17" s="155"/>
@@ -32813,7 +32814,7 @@
     </row>
     <row r="18" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="297" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C18" s="297"/>
       <c r="D18" s="150"/>
@@ -33332,7 +33333,7 @@
     </row>
     <row r="20" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B20" s="298" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C20" s="298"/>
       <c r="D20" s="152"/>
@@ -33591,7 +33592,7 @@
     </row>
     <row r="21" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" s="298" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C21" s="298"/>
       <c r="D21" s="152"/>
@@ -33850,7 +33851,7 @@
     </row>
     <row r="22" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" s="298" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C22" s="298"/>
       <c r="D22" s="152"/>
@@ -34109,7 +34110,7 @@
     </row>
     <row r="23" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B23" s="298" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C23" s="298"/>
       <c r="D23" s="152"/>
@@ -34356,7 +34357,7 @@
     </row>
     <row r="24" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B24" s="298" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24" s="298"/>
       <c r="D24" s="152"/>
@@ -34850,7 +34851,7 @@
     </row>
     <row r="26" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="300" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C26" s="300"/>
       <c r="D26" s="153"/>
@@ -35097,7 +35098,7 @@
     </row>
     <row r="27" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="300" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C27" s="300"/>
       <c r="D27" s="154"/>
@@ -35350,11 +35351,11 @@
     </row>
     <row r="29" spans="2:77" s="86" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="291" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C29" s="291"/>
       <c r="D29" s="145" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E29" s="156">
         <f>'Project Infor'!C8</f>
@@ -35612,7 +35613,7 @@
     </row>
     <row r="30" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="297" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C30" s="297"/>
       <c r="D30" s="150">
@@ -36137,7 +36138,7 @@
     </row>
     <row r="32" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="298" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C32" s="298"/>
       <c r="D32" s="158">
@@ -36399,7 +36400,7 @@
     </row>
     <row r="33" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="298" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C33" s="298"/>
       <c r="D33" s="158"/>
@@ -36658,7 +36659,7 @@
     </row>
     <row r="34" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="298" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C34" s="298"/>
       <c r="D34" s="158"/>
@@ -36917,7 +36918,7 @@
     </row>
     <row r="35" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="298" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C35" s="298"/>
       <c r="D35" s="158">
@@ -37167,7 +37168,7 @@
     </row>
     <row r="36" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" s="298" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C36" s="298"/>
       <c r="D36" s="158">
@@ -37415,7 +37416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="298" t="s">
         <v>65</v>
       </c>
@@ -37667,7 +37668,7 @@
     </row>
     <row r="38" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="299" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C38" s="299"/>
       <c r="D38" s="159">
@@ -37979,7 +37980,7 @@
     </row>
     <row r="40" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="301" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C40" s="301"/>
       <c r="D40" s="161"/>
@@ -38301,7 +38302,7 @@
     </row>
     <row r="42" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="301" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C42" s="301"/>
       <c r="D42" s="161">
@@ -38383,7 +38384,7 @@
     </row>
     <row r="43" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="300" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C43" s="300"/>
       <c r="D43" s="153">
@@ -38633,7 +38634,7 @@
     </row>
     <row r="44" spans="2:77" s="67" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="300" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C44" s="300"/>
       <c r="D44" s="160"/>
@@ -40408,10 +40409,10 @@
         <v>65</v>
       </c>
       <c r="L5" s="205" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M5" s="208" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N5" s="208" t="s">
         <v>67</v>
@@ -40421,7 +40422,7 @@
     </row>
     <row r="6" spans="2:16" s="89" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="306" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C6" s="307"/>
       <c r="D6" s="202">
@@ -40473,7 +40474,7 @@
     </row>
     <row r="7" spans="2:16" s="89" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="308" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C7" s="308"/>
       <c r="D7" s="209">
@@ -40525,7 +40526,7 @@
     </row>
     <row r="8" spans="2:16" s="89" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="308" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" s="308"/>
       <c r="D8" s="209">
@@ -40577,43 +40578,43 @@
     </row>
     <row r="9" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="309" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" s="309"/>
       <c r="D9" s="211">
-        <f>IF(D8=0,1,(D8-D7)/D8)</f>
+        <f>IF(AND(D8=0,D7=0),0,IF(D8=0,1,(D8-D7)/D8))</f>
         <v>0</v>
       </c>
       <c r="E9" s="211">
-        <f t="shared" ref="E9:L9" si="0">IF(E8=0,1,(E8-E7)/E8)</f>
+        <f>IF(AND(E8=0,E7=0),0,IF(E8=0,1,(E8-E7)/E8))</f>
         <v>-7.8120534355124018E-9</v>
       </c>
       <c r="F9" s="211">
-        <f t="shared" si="0"/>
+        <f>IF(AND(F8=0,F7=0),0,IF(F8=0,1,(F8-F7)/F8))</f>
         <v>0</v>
       </c>
       <c r="G9" s="211">
-        <f t="shared" si="0"/>
+        <f>IF(AND(G8=0,G7=0),0,IF(G8=0,1,(G8-G7)/G8))</f>
         <v>0</v>
       </c>
       <c r="H9" s="211">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(AND(H8=0,H7=0),0,IF(H8=0,1,(H8-H7)/H8))</f>
+        <v>0</v>
       </c>
       <c r="I9" s="211">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(AND(I8=0,I7=0),0,IF(I8=0,1,(I8-I7)/I8))</f>
+        <v>0</v>
       </c>
       <c r="J9" s="211">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(AND(J8=0,J7=0),0,IF(J8=0,1,(J8-J7)/J8))</f>
+        <v>0</v>
       </c>
       <c r="K9" s="211">
-        <f t="shared" si="0"/>
+        <f>IF(AND(K8=0,K7=0),0,IF(K8=0,1,(K8-K7)/K8))</f>
         <v>-7.7347063368341113E-9</v>
       </c>
       <c r="L9" s="211">
-        <f t="shared" si="0"/>
+        <f>IF(AND(L8=0,L7=0),0,IF(L8=0,1,(L8-L7)/L8))</f>
         <v>2.6568221847162273E-8</v>
       </c>
       <c r="M9" s="212">
@@ -40643,7 +40644,7 @@
     </row>
     <row r="11" spans="2:16" s="89" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="307" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C11" s="307"/>
       <c r="D11" s="202">
@@ -40695,7 +40696,7 @@
     </row>
     <row r="12" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="305" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C12" s="305"/>
       <c r="D12" s="165">
@@ -40730,7 +40731,7 @@
     </row>
     <row r="17" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="65" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C17" s="65"/>
       <c r="D17" s="65"/>
@@ -40749,7 +40750,7 @@
     </row>
     <row r="18" spans="2:16" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="302" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C18" s="303"/>
       <c r="D18" s="303"/>
@@ -40803,7 +40804,7 @@
     <row r="1" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="324" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C2" s="324"/>
       <c r="D2" s="324"/>
@@ -40811,32 +40812,32 @@
     <row r="3" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="174" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="175" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="175" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="175" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="175" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="175" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -40844,73 +40845,73 @@
     </row>
     <row r="11" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="174" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="175" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="175" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="175" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="175" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="175" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="175" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="175" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="174" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="175" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="175" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="175" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="175" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="175" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -40992,7 +40993,7 @@
     </row>
     <row r="5" spans="2:24" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="248" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C5" s="248"/>
       <c r="D5" s="248"/>
@@ -41001,7 +41002,7 @@
         <v>465000</v>
       </c>
       <c r="F5" s="326" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G5" s="326"/>
       <c r="H5" s="326"/>
@@ -41034,49 +41035,49 @@
     </row>
     <row r="7" spans="2:24" s="252" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="236" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="236" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="236" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="236" t="s">
+      <c r="E7" s="236" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="236" t="s">
+      <c r="F7" s="237" t="s">
         <v>222</v>
       </c>
-      <c r="E7" s="236" t="s">
+      <c r="G7" s="237" t="s">
         <v>223</v>
       </c>
-      <c r="F7" s="237" t="s">
+      <c r="H7" s="236" t="s">
         <v>224</v>
       </c>
-      <c r="G7" s="237" t="s">
+      <c r="I7" s="236" t="s">
         <v>225</v>
       </c>
-      <c r="H7" s="236" t="s">
+      <c r="J7" s="236" t="s">
         <v>226</v>
       </c>
-      <c r="I7" s="236" t="s">
+      <c r="K7" s="236" t="s">
         <v>227</v>
       </c>
-      <c r="J7" s="236" t="s">
+      <c r="L7" s="236" t="s">
         <v>228</v>
       </c>
-      <c r="K7" s="236" t="s">
+      <c r="M7" s="237" t="s">
         <v>229</v>
       </c>
-      <c r="L7" s="236" t="s">
+      <c r="N7" s="237" t="s">
         <v>230</v>
       </c>
-      <c r="M7" s="237" t="s">
+      <c r="O7" s="237" t="s">
         <v>231</v>
       </c>
-      <c r="N7" s="237" t="s">
+      <c r="P7" s="237" t="s">
         <v>232</v>
-      </c>
-      <c r="O7" s="237" t="s">
-        <v>233</v>
-      </c>
-      <c r="P7" s="237" t="s">
-        <v>234</v>
       </c>
       <c r="Q7" s="247"/>
       <c r="R7" s="240"/>
@@ -42112,7 +42113,7 @@
     </row>
     <row r="41" spans="2:24" s="254" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="325" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C41" s="325"/>
       <c r="D41" s="325"/>
@@ -42267,7 +42268,7 @@
     <row r="48" spans="2:24" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" spans="2:19" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
@@ -42374,7 +42375,7 @@
     <row r="3" spans="2:40" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:40" s="86" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="145" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C4" s="146">
         <v>44197</v>
@@ -42943,7 +42944,7 @@
     <row r="18" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="65" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="65"/>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-e08-review\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-rpa-validacion\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14182B84-3424-4F58-AD69-AF528E0228C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74B67A3-6A6A-49CB-A254-348C7EA28637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Infor" sheetId="1" r:id="rId1"/>
@@ -1123,7 +1123,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>Generado por RPA: 2026-05-11 10:50:00 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 00:26:08 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>
@@ -7631,7 +7631,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="54">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="D5" s="62"/>
       <c r="E5" s="60"/>
@@ -16227,148 +16227,148 @@
         <v>92</v>
       </c>
       <c r="G8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="H8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="I8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="J8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="K8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="L8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="M8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="N8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="O8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="P8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="Q8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="R8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="S8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="T8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="U8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="V8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="W8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="X8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="Y8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="Z8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AA8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AB8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AC8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AD8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AE8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AF8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AG8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AH8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AI8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AJ8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AK8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AL8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AM8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AN8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AO8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AP8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AQ8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AR8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AS8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AT8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AU8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AV8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AW8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AX8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AY8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="AZ8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="BA8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="BB8">
-        <v>44.790488927572149</v>
+        <v>44.790489000000001</v>
       </c>
       <c r="BC8" s="266"/>
       <c r="BD8" s="266"/>
@@ -16597,148 +16597,148 @@
         <v>92</v>
       </c>
       <c r="G10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="H10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="I10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="J10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="K10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="L10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="M10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="N10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="O10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="P10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="Q10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="R10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="S10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="T10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="U10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="V10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="W10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="X10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="Y10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="Z10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AA10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AB10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AC10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AD10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AE10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AF10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AG10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AH10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AI10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AJ10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AK10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AL10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AM10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AN10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AO10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AP10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AQ10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AR10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AS10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AT10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AU10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AV10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AW10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AX10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AY10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="AZ10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="BA10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="BB10">
-        <v>20.690361997956153</v>
+        <v>20.690362</v>
       </c>
       <c r="BC10" s="266"/>
       <c r="BD10" s="266"/>
@@ -16967,148 +16967,148 @@
         <v>92</v>
       </c>
       <c r="G12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="H12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="I12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="J12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="K12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="L12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="M12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="N12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="O12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="P12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="Q12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="R12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="S12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="T12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="U12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="V12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="W12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="X12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="Y12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="Z12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AA12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AB12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AC12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AD12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AE12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AF12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AG12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AH12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AI12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AJ12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AK12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AL12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AM12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AN12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AO12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AP12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AQ12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AR12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AS12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AT12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AU12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AV12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AW12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AX12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AY12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="AZ12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="BA12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="BB12">
-        <v>27.279471096621165</v>
+        <v>27.279471000000001</v>
       </c>
       <c r="BC12" s="266"/>
       <c r="BD12" s="266"/>
@@ -20672,7 +20672,7 @@
       <c r="M5" s="113"/>
       <c r="N5" s="114">
         <f>-(pedidobaselineactual-SUM(H44:BO44)-SUM(H62:BO62)-SUM(H78:BO78))</f>
-        <v>0</v>
+        <v>4.8799993237480521E-4</v>
       </c>
       <c r="O5" s="229"/>
       <c r="P5" s="229"/>
@@ -24979,195 +24979,195 @@
       <c r="G44" s="120"/>
       <c r="H44" s="282" cm="1">
         <f t="array" ref="H44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,H$10:H$39,Resources!G7:G36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="I44" s="282" cm="1">
         <f t="array" ref="I44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,I$10:I$39,Resources!H7:H36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="J44" s="282" cm="1">
         <f t="array" ref="J44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,J$10:J$39,Resources!I7:I36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="K44" s="282" cm="1">
         <f t="array" ref="K44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,K$10:K$39,Resources!J7:J36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="L44" s="282" cm="1">
         <f t="array" ref="L44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,L$10:L$39,Resources!K7:K36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="M44" s="282" cm="1">
         <f t="array" ref="M44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,M$10:M$39,Resources!L7:L36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="N44" s="282" cm="1">
         <f t="array" ref="N44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,N$10:N$39,Resources!M7:M36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="O44" s="282" cm="1">
         <f t="array" ref="O44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,O$10:O$39,Resources!N7:N36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="P44" s="282" cm="1">
         <f t="array" ref="P44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,P$10:P$39,Resources!O7:O36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="Q44" s="282" cm="1">
         <f t="array" ref="Q44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,Q$10:Q$39,Resources!P7:P36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="R44" s="282" cm="1">
         <f t="array" ref="R44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,R$10:R$39,Resources!Q7:Q36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="S44" s="282" cm="1">
         <f t="array" ref="S44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,S$10:S$39,Resources!R7:R36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="T44" s="282" cm="1">
         <f t="array" ref="T44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,T$10:T$39,Resources!S7:S36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="U44" s="282" cm="1">
         <f t="array" ref="U44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,U$10:U$39,Resources!T7:T36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="V44" s="282" cm="1">
         <f t="array" ref="V44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,V$10:V$39,Resources!U7:U36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="W44" s="282" cm="1">
         <f t="array" ref="W44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,W$10:W$39,Resources!V7:V36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="X44" s="282" cm="1">
         <f t="array" ref="X44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,X$10:X$39,Resources!W7:W36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="Y44" s="282" cm="1">
         <f t="array" ref="Y44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,Y$10:Y$39,Resources!X7:X36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="Z44" s="282" cm="1">
         <f t="array" ref="Z44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,Z$10:Z$39,Resources!Y7:Y36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AA44" s="282" cm="1">
         <f t="array" ref="AA44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AA$10:AA$39,Resources!Z7:Z36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AB44" s="282" cm="1">
         <f t="array" ref="AB44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AB$10:AB$39,Resources!AA7:AA36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AC44" s="282" cm="1">
         <f t="array" ref="AC44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AC$10:AC$39,Resources!AB7:AB36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AD44" s="282" cm="1">
         <f t="array" ref="AD44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AD$10:AD$39,Resources!AC7:AC36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AE44" s="282" cm="1">
         <f t="array" ref="AE44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AE$10:AE$39,Resources!AD7:AD36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AF44" s="282" cm="1">
         <f t="array" ref="AF44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AF$10:AF$39,Resources!AE7:AE36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AG44" s="282" cm="1">
         <f t="array" ref="AG44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AG$10:AG$39,Resources!AF7:AF36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AH44" s="282" cm="1">
         <f t="array" ref="AH44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AH$10:AH$39,Resources!AG7:AG36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AI44" s="282" cm="1">
         <f t="array" ref="AI44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AI$10:AI$39,Resources!AH7:AH36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AJ44" s="282" cm="1">
         <f t="array" ref="AJ44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AJ$10:AJ$39,Resources!AI7:AI36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AK44" s="282" cm="1">
         <f t="array" ref="AK44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AK$10:AK$39,Resources!AJ7:AJ36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AL44" s="282" cm="1">
         <f t="array" ref="AL44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AL$10:AL$39,Resources!AK7:AK36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AM44" s="282" cm="1">
         <f t="array" ref="AM44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AM$10:AM$39,Resources!AL7:AL36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AN44" s="282" cm="1">
         <f t="array" ref="AN44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AN$10:AN$39,Resources!AM7:AM36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AO44" s="282" cm="1">
         <f t="array" ref="AO44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AO$10:AO$39,Resources!AN7:AN36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AP44" s="282" cm="1">
         <f t="array" ref="AP44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AP$10:AP$39,Resources!AO7:AO36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AQ44" s="282" cm="1">
         <f t="array" ref="AQ44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AQ$10:AQ$39,Resources!AP7:AP36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AR44" s="282" cm="1">
         <f t="array" ref="AR44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AR$10:AR$39,Resources!AQ7:AQ36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AS44" s="282" cm="1">
         <f t="array" ref="AS44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AS$10:AS$39,Resources!AR7:AR36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AT44" s="282" cm="1">
         <f t="array" ref="AT44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AT$10:AT$39,Resources!AS7:AS36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AU44" s="282" cm="1">
         <f t="array" ref="AU44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AU$10:AU$39,Resources!AT7:AT36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AV44" s="282" cm="1">
         <f t="array" ref="AV44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AV$10:AV$39,Resources!AU7:AU36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AW44" s="282" cm="1">
         <f t="array" ref="AW44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AW$10:AW$39,Resources!AV7:AV36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AX44" s="282" cm="1">
         <f t="array" ref="AX44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AX$10:AX$39,Resources!AW7:AW36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AY44" s="282" cm="1">
         <f t="array" ref="AY44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AY$10:AY$39,Resources!AX7:AX36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AZ44" s="282" cm="1">
         <f t="array" ref="AZ44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,AZ$10:AZ$39,Resources!AY7:AY36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="BA44" s="282" cm="1">
         <f t="array" ref="BA44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BA$10:BA$39,Resources!AZ7:AZ36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="BB44" s="282" cm="1">
         <f t="array" ref="BB44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BB$10:BB$39,Resources!BA7:BA36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="BC44" s="282" cm="1">
         <f t="array" ref="BC44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BC$10:BC$39,Resources!BB7:BB36)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="BD44" s="282" cm="1">
         <f t="array" ref="BD44">SUMPRODUCT(($G$10:$G$39="Horas/Jornadas Facturables")*1,BD$10:BD$39,Resources!BC7:BC36)</f>
@@ -29516,7 +29516,7 @@
       <c r="L2" s="294"/>
       <c r="M2" s="168">
         <f>'Cost Planning'!N5</f>
-        <v>0</v>
+        <v>4.8799993237480521E-4</v>
       </c>
     </row>
     <row r="3" spans="2:77" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -32820,195 +32820,195 @@
       <c r="D18" s="150"/>
       <c r="E18" s="150">
         <f>'Cost Planning'!H44+'Cost Planning'!H62+'Cost Planning'!H78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="F18" s="150">
         <f>'Cost Planning'!I44+'Cost Planning'!I62+'Cost Planning'!I78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="G18" s="150">
         <f>'Cost Planning'!J44+'Cost Planning'!J62+'Cost Planning'!J78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="H18" s="150">
         <f>'Cost Planning'!K44+'Cost Planning'!K62+'Cost Planning'!K78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="I18" s="150">
         <f>'Cost Planning'!L44+'Cost Planning'!L62+'Cost Planning'!L78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="J18" s="150">
         <f>'Cost Planning'!M44+'Cost Planning'!M62+'Cost Planning'!M78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="K18" s="150">
         <f>'Cost Planning'!N44+'Cost Planning'!N62+'Cost Planning'!N78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="L18" s="150">
         <f>'Cost Planning'!O44+'Cost Planning'!O62+'Cost Planning'!O78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="M18" s="150">
         <f>'Cost Planning'!P44+'Cost Planning'!P62+'Cost Planning'!P78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="N18" s="150">
         <f>'Cost Planning'!Q44+'Cost Planning'!Q62+'Cost Planning'!Q78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="O18" s="150">
         <f>'Cost Planning'!R44+'Cost Planning'!R62+'Cost Planning'!R78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="P18" s="150">
         <f>'Cost Planning'!S44+'Cost Planning'!S62+'Cost Planning'!S78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="Q18" s="150">
         <f>'Cost Planning'!T44+'Cost Planning'!T62+'Cost Planning'!T78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="R18" s="150">
         <f>'Cost Planning'!U44+'Cost Planning'!U62+'Cost Planning'!U78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="S18" s="150">
         <f>'Cost Planning'!V44+'Cost Planning'!V62+'Cost Planning'!V78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="T18" s="150">
         <f>'Cost Planning'!W44+'Cost Planning'!W62+'Cost Planning'!W78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="U18" s="150">
         <f>'Cost Planning'!X44+'Cost Planning'!X62+'Cost Planning'!X78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="V18" s="150">
         <f>'Cost Planning'!Y44+'Cost Planning'!Y62+'Cost Planning'!Y78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="W18" s="150">
         <f>'Cost Planning'!Z44+'Cost Planning'!Z62+'Cost Planning'!Z78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="X18" s="150">
         <f>'Cost Planning'!AA44+'Cost Planning'!AA62+'Cost Planning'!AA78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="Y18" s="150">
         <f>'Cost Planning'!AB44+'Cost Planning'!AB62+'Cost Planning'!AB78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="Z18" s="150">
         <f>'Cost Planning'!AC44+'Cost Planning'!AC62+'Cost Planning'!AC78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AA18" s="150">
         <f>'Cost Planning'!AD44+'Cost Planning'!AD62+'Cost Planning'!AD78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AB18" s="150">
         <f>'Cost Planning'!AE44+'Cost Planning'!AE62+'Cost Planning'!AE78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AC18" s="150">
         <f>'Cost Planning'!AF44+'Cost Planning'!AF62+'Cost Planning'!AF78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AD18" s="150">
         <f>'Cost Planning'!AG44+'Cost Planning'!AG62+'Cost Planning'!AG78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AE18" s="150">
         <f>'Cost Planning'!AH44+'Cost Planning'!AH62+'Cost Planning'!AH78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AF18" s="150">
         <f>'Cost Planning'!AI44+'Cost Planning'!AI62+'Cost Planning'!AI78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AG18" s="150">
         <f>'Cost Planning'!AJ44+'Cost Planning'!AJ62+'Cost Planning'!AJ78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AH18" s="150">
         <f>'Cost Planning'!AK44+'Cost Planning'!AK62+'Cost Planning'!AK78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AI18" s="150">
         <f>'Cost Planning'!AL44+'Cost Planning'!AL62+'Cost Planning'!AL78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AJ18" s="150">
         <f>'Cost Planning'!AM44+'Cost Planning'!AM62+'Cost Planning'!AM78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AK18" s="150">
         <f>'Cost Planning'!AN44+'Cost Planning'!AN62+'Cost Planning'!AN78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AL18" s="150">
         <f>'Cost Planning'!AO44+'Cost Planning'!AO62+'Cost Planning'!AO78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AM18" s="150">
         <f>'Cost Planning'!AP44+'Cost Planning'!AP62+'Cost Planning'!AP78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AN18" s="150">
         <f>'Cost Planning'!AQ44+'Cost Planning'!AQ62+'Cost Planning'!AQ78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AO18" s="150">
         <f>'Cost Planning'!AR44+'Cost Planning'!AR62+'Cost Planning'!AR78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AP18" s="150">
         <f>'Cost Planning'!AS44+'Cost Planning'!AS62+'Cost Planning'!AS78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AQ18" s="150">
         <f>'Cost Planning'!AT44+'Cost Planning'!AT62+'Cost Planning'!AT78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AR18" s="150">
         <f>'Cost Planning'!AU44+'Cost Planning'!AU62+'Cost Planning'!AU78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AS18" s="150">
         <f>'Cost Planning'!AV44+'Cost Planning'!AV62+'Cost Planning'!AV78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AT18" s="150">
         <f>'Cost Planning'!AW44+'Cost Planning'!AW62+'Cost Planning'!AW78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AU18" s="150">
         <f>'Cost Planning'!AX44+'Cost Planning'!AX62+'Cost Planning'!AX78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AV18" s="150">
         <f>'Cost Planning'!AY44+'Cost Planning'!AY62+'Cost Planning'!AY78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AW18" s="150">
         <f>'Cost Planning'!AZ44+'Cost Planning'!AZ62+'Cost Planning'!AZ78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AX18" s="150">
         <f>'Cost Planning'!BA44+'Cost Planning'!BA62+'Cost Planning'!BA78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AY18" s="150">
         <f>'Cost Planning'!BB44+'Cost Planning'!BB62+'Cost Planning'!BB78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="AZ18" s="150">
         <f>'Cost Planning'!BC44+'Cost Planning'!BC62+'Cost Planning'!BC78</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="BA18" s="150">
         <f>'Cost Planning'!BD44+'Cost Planning'!BD62+'Cost Planning'!BD78</f>
@@ -34857,195 +34857,195 @@
       <c r="D26" s="153"/>
       <c r="E26" s="153">
         <f>E18-E25</f>
-        <v>2584.7150000000001</v>
+        <v>2584.7150101666648</v>
       </c>
       <c r="F26" s="157">
         <f t="shared" ref="F26:Z26" si="150">F18-F25</f>
-        <v>2584.7150000000001</v>
+        <v>2584.7150101666648</v>
       </c>
       <c r="G26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7150000000001</v>
+        <v>2584.7150101666648</v>
       </c>
       <c r="H26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7150000000001</v>
+        <v>2584.7150101666648</v>
       </c>
       <c r="I26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="J26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="K26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="L26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="M26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="N26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="O26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="P26" s="157">
         <f t="shared" si="150"/>
-        <v>2584.7149999999965</v>
+        <v>2584.7150101666612</v>
       </c>
       <c r="Q26" s="157">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="R26" s="157">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="S26" s="157">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="T26" s="157">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="U26" s="157">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="V26" s="153">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="W26" s="153">
         <f t="shared" si="150"/>
-        <v>2371.6314500000008</v>
+        <v>2371.6314601666654</v>
       </c>
       <c r="X26" s="153">
         <f t="shared" si="150"/>
-        <v>2371.6314499999862</v>
+        <v>2371.6314601666509</v>
       </c>
       <c r="Y26" s="153">
         <f t="shared" si="150"/>
-        <v>2371.6314499999862</v>
+        <v>2371.6314601666509</v>
       </c>
       <c r="Z26" s="153">
         <f t="shared" si="150"/>
-        <v>2371.6314499999862</v>
+        <v>2371.6314601666509</v>
       </c>
       <c r="AA26" s="153">
         <f>AA18-AA25</f>
-        <v>2371.6314499999862</v>
+        <v>2371.6314601666509</v>
       </c>
       <c r="AB26" s="153">
         <f>AB18-AB25</f>
-        <v>2371.6314499999862</v>
+        <v>2371.6314601666509</v>
       </c>
       <c r="AC26" s="153">
         <f t="shared" ref="AC26:BL26" si="151">AC18-AC25</f>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AD26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AE26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AF26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AG26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AH26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AI26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AJ26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AK26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AL26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AM26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AN26" s="153">
         <f t="shared" si="151"/>
-        <v>2152.1553934999974</v>
+        <v>2152.1554036666621</v>
       </c>
       <c r="AO26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AP26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AQ26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AR26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AS26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AT26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AU26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AV26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AW26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AX26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AY26" s="153">
         <f t="shared" si="151"/>
-        <v>1926.0950553049915</v>
+        <v>1926.0950654716562</v>
       </c>
       <c r="AZ26" s="153">
         <f t="shared" si="151"/>
-        <v>-1639.7549446950088</v>
+        <v>-1639.7549345283442</v>
       </c>
       <c r="BA26" s="153">
         <f t="shared" si="151"/>
@@ -35104,195 +35104,195 @@
       <c r="D27" s="154"/>
       <c r="E27" s="154">
         <f>IF(E18=0,0,(E18-SUM(E20,E21,E22,E23,E24))/E18)</f>
-        <v>0.26680929032258066</v>
+        <v>0.26680929109203655</v>
       </c>
       <c r="F27" s="154">
         <f t="shared" ref="F27:Z27" si="152">IF(F18=0,0,(F18-SUM(F20,F21,F22,F23,F24))/F18)</f>
-        <v>0.26680929032258066</v>
+        <v>0.26680929109203655</v>
       </c>
       <c r="G27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258066</v>
+        <v>0.26680929109203655</v>
       </c>
       <c r="H27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258066</v>
+        <v>0.26680929109203655</v>
       </c>
       <c r="I27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="J27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="K27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="L27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="M27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="N27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="O27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="P27" s="154">
         <f t="shared" si="152"/>
-        <v>0.26680929032258027</v>
+        <v>0.26680929109203616</v>
       </c>
       <c r="Q27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="R27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="S27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="T27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="U27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="V27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="W27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225815</v>
+        <v>0.24481356982479771</v>
       </c>
       <c r="X27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225665</v>
+        <v>0.24481356982479621</v>
       </c>
       <c r="Y27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225665</v>
+        <v>0.24481356982479621</v>
       </c>
       <c r="Z27" s="154">
         <f t="shared" si="152"/>
-        <v>0.24481356903225665</v>
+        <v>0.24481356982479621</v>
       </c>
       <c r="AA27" s="154">
         <f>IF(AA18=0,0,(AA18-SUM(AA20,AA21,AA22,AA23,AA24))/AA18)</f>
-        <v>0.24481356903225665</v>
+        <v>0.24481356982479621</v>
       </c>
       <c r="AB27" s="154">
         <f>IF(AB18=0,0,(AB18-SUM(AB20,AB21,AB22,AB23,AB24))/AB18)</f>
-        <v>0.24481356903225665</v>
+        <v>0.24481356982479621</v>
       </c>
       <c r="AC27" s="154">
         <f t="shared" ref="AC27:BL27" si="153">IF(AC18=0,0,(AC18-SUM(AC20,AC21,AC22,AC23,AC24))/AC18)</f>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AD27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AE27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AF27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AG27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AH27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AI27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AJ27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AK27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AL27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AM27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AN27" s="154">
         <f t="shared" si="153"/>
-        <v>0.22215797610322555</v>
+        <v>0.22215797691954131</v>
       </c>
       <c r="AO27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AP27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AQ27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AR27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AS27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AT27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AU27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AV27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AW27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AX27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AY27" s="154">
         <f t="shared" si="153"/>
-        <v>0.19882271538632171</v>
+        <v>0.19882271622712694</v>
       </c>
       <c r="AZ27" s="154">
         <f t="shared" si="153"/>
-        <v>-0.1692650265491622</v>
+        <v>-0.16926502532206281</v>
       </c>
       <c r="BA27" s="154">
         <f t="shared" si="153"/>
@@ -35622,191 +35622,191 @@
       </c>
       <c r="E30" s="150">
         <f t="shared" ref="E30:AB30" ca="1" si="213">IF(E40,E40,D30+E18)</f>
-        <v>9687.5</v>
+        <v>9687.5000101666647</v>
       </c>
       <c r="F30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>19375</v>
+        <v>19375.000020333329</v>
       </c>
       <c r="G30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>29062.5</v>
+        <v>29062.500030499992</v>
       </c>
       <c r="H30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>38750</v>
+        <v>38750.000040666659</v>
       </c>
       <c r="I30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>48437.5</v>
+        <v>48437.500050833325</v>
       </c>
       <c r="J30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>58125</v>
+        <v>58125.000060999992</v>
       </c>
       <c r="K30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>67812.5</v>
+        <v>67812.500071166651</v>
       </c>
       <c r="L30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>77500</v>
+        <v>77500.000081333317</v>
       </c>
       <c r="M30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>87187.5</v>
+        <v>87187.500091499984</v>
       </c>
       <c r="N30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>96875</v>
+        <v>96875.00010166665</v>
       </c>
       <c r="O30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>106562.5</v>
+        <v>106562.50011183332</v>
       </c>
       <c r="P30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>116250</v>
+        <v>116250.00012199998</v>
       </c>
       <c r="Q30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>125937.5</v>
+        <v>125937.50013216665</v>
       </c>
       <c r="R30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>135625</v>
+        <v>135625.0001423333</v>
       </c>
       <c r="S30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>145312.5</v>
+        <v>145312.50015249997</v>
       </c>
       <c r="T30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>155000</v>
+        <v>155000.00016266663</v>
       </c>
       <c r="U30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>164687.5</v>
+        <v>164687.5001728333</v>
       </c>
       <c r="V30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>174375</v>
+        <v>174375.00018299997</v>
       </c>
       <c r="W30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>184062.5</v>
+        <v>184062.50019316663</v>
       </c>
       <c r="X30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>193750</v>
+        <v>193750.0002033333</v>
       </c>
       <c r="Y30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>203437.5</v>
+        <v>203437.50021349997</v>
       </c>
       <c r="Z30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>213125</v>
+        <v>213125.00022366663</v>
       </c>
       <c r="AA30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>222812.5</v>
+        <v>222812.5002338333</v>
       </c>
       <c r="AB30" s="150">
         <f t="shared" ca="1" si="213"/>
-        <v>232500</v>
+        <v>232500.00024399997</v>
       </c>
       <c r="AC30" s="150">
         <f t="shared" ref="AC30" ca="1" si="214">IF(AC40,AC40,AB30+AC18)</f>
-        <v>242187.5</v>
+        <v>242187.50025416663</v>
       </c>
       <c r="AD30" s="150">
         <f t="shared" ref="AD30" ca="1" si="215">IF(AD40,AD40,AC30+AD18)</f>
-        <v>251875</v>
+        <v>251875.0002643333</v>
       </c>
       <c r="AE30" s="150">
         <f t="shared" ref="AE30" ca="1" si="216">IF(AE40,AE40,AD30+AE18)</f>
-        <v>261562.5</v>
+        <v>261562.50027449997</v>
       </c>
       <c r="AF30" s="150">
         <f t="shared" ref="AF30" ca="1" si="217">IF(AF40,AF40,AE30+AF18)</f>
-        <v>271250</v>
+        <v>271250.0002846666</v>
       </c>
       <c r="AG30" s="150">
         <f t="shared" ref="AG30" ca="1" si="218">IF(AG40,AG40,AF30+AG18)</f>
-        <v>280937.5</v>
+        <v>280937.50029483327</v>
       </c>
       <c r="AH30" s="150">
         <f t="shared" ref="AH30" ca="1" si="219">IF(AH40,AH40,AG30+AH18)</f>
-        <v>290625</v>
+        <v>290625.00030499994</v>
       </c>
       <c r="AI30" s="150">
         <f t="shared" ref="AI30" ca="1" si="220">IF(AI40,AI40,AH30+AI18)</f>
-        <v>300312.5</v>
+        <v>300312.5003151666</v>
       </c>
       <c r="AJ30" s="150">
         <f t="shared" ref="AJ30" ca="1" si="221">IF(AJ40,AJ40,AI30+AJ18)</f>
-        <v>310000</v>
+        <v>310000.00032533327</v>
       </c>
       <c r="AK30" s="150">
         <f t="shared" ref="AK30" ca="1" si="222">IF(AK40,AK40,AJ30+AK18)</f>
-        <v>319687.5</v>
+        <v>319687.50033549994</v>
       </c>
       <c r="AL30" s="150">
         <f t="shared" ref="AL30" ca="1" si="223">IF(AL40,AL40,AK30+AL18)</f>
-        <v>329375</v>
+        <v>329375.0003456666</v>
       </c>
       <c r="AM30" s="150">
         <f t="shared" ref="AM30" ca="1" si="224">IF(AM40,AM40,AL30+AM18)</f>
-        <v>339062.5</v>
+        <v>339062.50035583327</v>
       </c>
       <c r="AN30" s="150">
         <f t="shared" ref="AN30" ca="1" si="225">IF(AN40,AN40,AM30+AN18)</f>
-        <v>348750</v>
+        <v>348750.00036599993</v>
       </c>
       <c r="AO30" s="150">
         <f t="shared" ref="AO30" ca="1" si="226">IF(AO40,AO40,AN30+AO18)</f>
-        <v>358437.5</v>
+        <v>358437.5003761666</v>
       </c>
       <c r="AP30" s="150">
         <f t="shared" ref="AP30" ca="1" si="227">IF(AP40,AP40,AO30+AP18)</f>
-        <v>368125</v>
+        <v>368125.00038633327</v>
       </c>
       <c r="AQ30" s="150">
         <f t="shared" ref="AQ30" ca="1" si="228">IF(AQ40,AQ40,AP30+AQ18)</f>
-        <v>377812.5</v>
+        <v>377812.50039649993</v>
       </c>
       <c r="AR30" s="150">
         <f t="shared" ref="AR30" ca="1" si="229">IF(AR40,AR40,AQ30+AR18)</f>
-        <v>387500</v>
+        <v>387500.0004066666</v>
       </c>
       <c r="AS30" s="150">
         <f t="shared" ref="AS30" ca="1" si="230">IF(AS40,AS40,AR30+AS18)</f>
-        <v>397187.5</v>
+        <v>397187.50041683327</v>
       </c>
       <c r="AT30" s="150">
         <f t="shared" ref="AT30" ca="1" si="231">IF(AT40,AT40,AS30+AT18)</f>
-        <v>406875</v>
+        <v>406875.00042699993</v>
       </c>
       <c r="AU30" s="150">
         <f t="shared" ref="AU30" ca="1" si="232">IF(AU40,AU40,AT30+AU18)</f>
-        <v>416562.5</v>
+        <v>416562.5004371666</v>
       </c>
       <c r="AV30" s="150">
         <f t="shared" ref="AV30" ca="1" si="233">IF(AV40,AV40,AU30+AV18)</f>
-        <v>426250</v>
+        <v>426250.00044733327</v>
       </c>
       <c r="AW30" s="150">
         <f t="shared" ref="AW30" ca="1" si="234">IF(AW40,AW40,AV30+AW18)</f>
-        <v>435937.5</v>
+        <v>435937.50045749993</v>
       </c>
       <c r="AX30" s="150">
         <f t="shared" ref="AX30" ca="1" si="235">IF(AX40,AX40,AW30+AX18)</f>
-        <v>445625</v>
+        <v>445625.0004676666</v>
       </c>
       <c r="AY30" s="150">
         <f t="shared" ref="AY30" ca="1" si="236">IF(AY40,AY40,AX30+AY18)</f>
-        <v>455312.5</v>
+        <v>455312.50047783327</v>
       </c>
       <c r="AZ30" s="150">
         <f t="shared" ref="AZ30" ca="1" si="237">IF(AZ40,AZ40,AY30+AZ18)</f>
@@ -37677,191 +37677,191 @@
       </c>
       <c r="E38" s="159">
         <f ca="1">E30-E32-E33-E34-E35-E36</f>
-        <v>2584.7150000000001</v>
+        <v>2584.7150101666648</v>
       </c>
       <c r="F38" s="159">
         <f t="shared" ref="F38:Z38" ca="1" si="252">F30-F32-F33-F34-F35-F36</f>
-        <v>5169.43</v>
+        <v>5169.4300203333296</v>
       </c>
       <c r="G38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>7754.1450000000004</v>
+        <v>7754.1450304999926</v>
       </c>
       <c r="H38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>10338.86</v>
+        <v>10338.860040666659</v>
       </c>
       <c r="I38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>12923.574999999997</v>
+        <v>12923.575050833322</v>
       </c>
       <c r="J38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>15508.289999999994</v>
+        <v>15508.290060999985</v>
       </c>
       <c r="K38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>18093.00499999999</v>
+        <v>18093.005071166641</v>
       </c>
       <c r="L38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>20677.719999999987</v>
+        <v>20677.720081333304</v>
       </c>
       <c r="M38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>23262.434999999983</v>
+        <v>23262.435091499967</v>
       </c>
       <c r="N38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>25847.14999999998</v>
+        <v>25847.15010166663</v>
       </c>
       <c r="O38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>28431.864999999976</v>
+        <v>28431.865111833293</v>
       </c>
       <c r="P38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>31016.579999999973</v>
+        <v>31016.580121999956</v>
       </c>
       <c r="Q38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>33388.211449999973</v>
+        <v>33388.211582166623</v>
       </c>
       <c r="R38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>35759.842899999974</v>
+        <v>35759.843042333276</v>
       </c>
       <c r="S38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>38131.474349999975</v>
+        <v>38131.474502499943</v>
       </c>
       <c r="T38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>40503.105799999976</v>
+        <v>40503.10596266661</v>
       </c>
       <c r="U38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>42874.737249999976</v>
+        <v>42874.737422833277</v>
       </c>
       <c r="V38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>45246.368699999977</v>
+        <v>45246.368882999945</v>
       </c>
       <c r="W38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>47618.000149999978</v>
+        <v>47618.000343166612</v>
       </c>
       <c r="X38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>49989.631599999964</v>
+        <v>49989.631803333265</v>
       </c>
       <c r="Y38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>52361.26304999995</v>
+        <v>52361.263263499917</v>
       </c>
       <c r="Z38" s="159">
         <f t="shared" ca="1" si="252"/>
-        <v>54732.894499999937</v>
+        <v>54732.89472366657</v>
       </c>
       <c r="AA38" s="159">
         <f ca="1">AA30-AA32-AA33-AA34-AA35-AA36</f>
-        <v>57104.525949999923</v>
+        <v>57104.526183833223</v>
       </c>
       <c r="AB38" s="159">
         <f ca="1">AB30-AB32-AB33-AB34-AB35-AB36</f>
-        <v>59476.157399999909</v>
+        <v>59476.157643999875</v>
       </c>
       <c r="AC38" s="159">
         <f t="shared" ref="AC38:BL38" ca="1" si="253">AC30-AC32-AC33-AC34-AC35-AC36</f>
-        <v>61628.312793499907</v>
+        <v>61628.313047666539</v>
       </c>
       <c r="AD38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>63780.468186999904</v>
+        <v>63780.468451333203</v>
       </c>
       <c r="AE38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>65932.623580499901</v>
+        <v>65932.623854999867</v>
       </c>
       <c r="AF38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>68084.778973999899</v>
+        <v>68084.779258666502</v>
       </c>
       <c r="AG38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>70236.934367499896</v>
+        <v>70236.934662333166</v>
       </c>
       <c r="AH38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>72389.089760999894</v>
+        <v>72389.09006599983</v>
       </c>
       <c r="AI38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>74541.245154499891</v>
+        <v>74541.245469666494</v>
       </c>
       <c r="AJ38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>76693.400547999889</v>
+        <v>76693.400873333158</v>
       </c>
       <c r="AK38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>78845.555941499886</v>
+        <v>78845.556276999821</v>
       </c>
       <c r="AL38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>80997.711334999884</v>
+        <v>80997.711680666485</v>
       </c>
       <c r="AM38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>83149.866728499881</v>
+        <v>83149.867084333149</v>
       </c>
       <c r="AN38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>85302.022121999878</v>
+        <v>85302.022487999813</v>
       </c>
       <c r="AO38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>87228.11717730487</v>
+        <v>87228.117553471471</v>
       </c>
       <c r="AP38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>89154.212232609862</v>
+        <v>89154.212618943129</v>
       </c>
       <c r="AQ38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>91080.307287914853</v>
+        <v>91080.307684414787</v>
       </c>
       <c r="AR38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>93006.402343219845</v>
+        <v>93006.402749886445</v>
       </c>
       <c r="AS38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>94932.497398524836</v>
+        <v>94932.497815358103</v>
       </c>
       <c r="AT38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>96858.592453829828</v>
+        <v>96858.592880829761</v>
       </c>
       <c r="AU38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>98784.687509134819</v>
+        <v>98784.687946301419</v>
       </c>
       <c r="AV38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>100710.78256443981</v>
+        <v>100710.78301177308</v>
       </c>
       <c r="AW38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>102636.8776197448</v>
+        <v>102636.87807724474</v>
       </c>
       <c r="AX38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>104562.97267504979</v>
+        <v>104562.97314271639</v>
       </c>
       <c r="AY38" s="159">
         <f t="shared" ca="1" si="253"/>
-        <v>106489.06773035479</v>
+        <v>106489.06820818805</v>
       </c>
       <c r="AZ38" s="159">
         <f t="shared" ca="1" si="253"/>
@@ -38640,191 +38640,191 @@
       <c r="D44" s="160"/>
       <c r="E44" s="160">
         <f t="shared" ref="E44:Z44" ca="1" si="294">E43-E30</f>
-        <v>-9687.5</v>
+        <v>-9687.5000101666647</v>
       </c>
       <c r="F44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-19375</v>
+        <v>-19375.000020333329</v>
       </c>
       <c r="G44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-29062.5</v>
+        <v>-29062.500030499992</v>
       </c>
       <c r="H44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-38750</v>
+        <v>-38750.000040666659</v>
       </c>
       <c r="I44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-48437.5</v>
+        <v>-48437.500050833325</v>
       </c>
       <c r="J44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-58125</v>
+        <v>-58125.000060999992</v>
       </c>
       <c r="K44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-67812.5</v>
+        <v>-67812.500071166651</v>
       </c>
       <c r="L44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-77500</v>
+        <v>-77500.000081333317</v>
       </c>
       <c r="M44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-87187.5</v>
+        <v>-87187.500091499984</v>
       </c>
       <c r="N44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-96875</v>
+        <v>-96875.00010166665</v>
       </c>
       <c r="O44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-106562.5</v>
+        <v>-106562.50011183332</v>
       </c>
       <c r="P44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-116250</v>
+        <v>-116250.00012199998</v>
       </c>
       <c r="Q44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-125937.5</v>
+        <v>-125937.50013216665</v>
       </c>
       <c r="R44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-135625</v>
+        <v>-135625.0001423333</v>
       </c>
       <c r="S44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-145312.5</v>
+        <v>-145312.50015249997</v>
       </c>
       <c r="T44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-155000</v>
+        <v>-155000.00016266663</v>
       </c>
       <c r="U44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-164687.5</v>
+        <v>-164687.5001728333</v>
       </c>
       <c r="V44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-174375</v>
+        <v>-174375.00018299997</v>
       </c>
       <c r="W44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-184062.5</v>
+        <v>-184062.50019316663</v>
       </c>
       <c r="X44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-193750</v>
+        <v>-193750.0002033333</v>
       </c>
       <c r="Y44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-203437.5</v>
+        <v>-203437.50021349997</v>
       </c>
       <c r="Z44" s="160">
         <f t="shared" ca="1" si="294"/>
-        <v>-213125</v>
+        <v>-213125.00022366663</v>
       </c>
       <c r="AA44" s="160">
         <f ca="1">AA43-AA30</f>
-        <v>-222812.5</v>
+        <v>-222812.5002338333</v>
       </c>
       <c r="AB44" s="160">
         <f ca="1">AB43-AB30</f>
-        <v>-232500</v>
+        <v>-232500.00024399997</v>
       </c>
       <c r="AC44" s="160">
         <f t="shared" ref="AC44:BL44" ca="1" si="295">AC43-AC30</f>
-        <v>-242187.5</v>
+        <v>-242187.50025416663</v>
       </c>
       <c r="AD44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-251875</v>
+        <v>-251875.0002643333</v>
       </c>
       <c r="AE44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-261562.5</v>
+        <v>-261562.50027449997</v>
       </c>
       <c r="AF44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-271250</v>
+        <v>-271250.0002846666</v>
       </c>
       <c r="AG44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-280937.5</v>
+        <v>-280937.50029483327</v>
       </c>
       <c r="AH44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-290625</v>
+        <v>-290625.00030499994</v>
       </c>
       <c r="AI44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-300312.5</v>
+        <v>-300312.5003151666</v>
       </c>
       <c r="AJ44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-310000</v>
+        <v>-310000.00032533327</v>
       </c>
       <c r="AK44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-319687.5</v>
+        <v>-319687.50033549994</v>
       </c>
       <c r="AL44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-329375</v>
+        <v>-329375.0003456666</v>
       </c>
       <c r="AM44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-339062.5</v>
+        <v>-339062.50035583327</v>
       </c>
       <c r="AN44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-348750</v>
+        <v>-348750.00036599993</v>
       </c>
       <c r="AO44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-358437.5</v>
+        <v>-358437.5003761666</v>
       </c>
       <c r="AP44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-368125</v>
+        <v>-368125.00038633327</v>
       </c>
       <c r="AQ44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-377812.5</v>
+        <v>-377812.50039649993</v>
       </c>
       <c r="AR44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-387500</v>
+        <v>-387500.0004066666</v>
       </c>
       <c r="AS44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-397187.5</v>
+        <v>-397187.50041683327</v>
       </c>
       <c r="AT44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-406875</v>
+        <v>-406875.00042699993</v>
       </c>
       <c r="AU44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-416562.5</v>
+        <v>-416562.5004371666</v>
       </c>
       <c r="AV44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-426250</v>
+        <v>-426250.00044733327</v>
       </c>
       <c r="AW44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-435937.5</v>
+        <v>-435937.50045749993</v>
       </c>
       <c r="AX44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-445625</v>
+        <v>-445625.0004676666</v>
       </c>
       <c r="AY44" s="160">
         <f t="shared" ca="1" si="295"/>
-        <v>-455312.5</v>
+        <v>-455312.50047783327</v>
       </c>
       <c r="AZ44" s="160">
         <f t="shared" ca="1" si="295"/>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-rpa-validacion\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\Documents\UiPath\oportunidad-generar-core-v3\oportunidad-generar-core-main\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74B67A3-6A6A-49CB-A254-348C7EA28637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9FD339-CB6D-4DC4-A0BA-BC566EC3CFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,7 +1123,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 00:26:08 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 01:04:41 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\Documents\UiPath\oportunidad-generar-core-v3\oportunidad-generar-core-main\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.38-ep1\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9FD339-CB6D-4DC4-A0BA-BC566EC3CFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359449EC-3436-4D92-9A48-D931A550B9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,7 +1123,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 01:04:41 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:12:49 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>
@@ -3072,6 +3072,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3081,16 +3088,9 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="D4" s="315"/>
       <c r="E4" s="22"/>
-      <c r="F4" s="332" t="s">
+      <c r="F4" s="328" t="s">
         <v>238</v>
       </c>
       <c r="G4" s="333"/>
@@ -9029,26 +9029,26 @@
       <c r="J4" s="228" t="s">
         <v>241</v>
       </c>
-      <c r="K4" s="332" t="s">
+      <c r="K4" s="328" t="s">
         <v>242</v>
       </c>
-      <c r="L4" s="332"/>
-      <c r="M4" s="332"/>
-      <c r="N4" s="332"/>
+      <c r="L4" s="328"/>
+      <c r="M4" s="328"/>
+      <c r="N4" s="328"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="77" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="330" t="s">
+      <c r="C5" s="327" t="s">
         <v>244</v>
       </c>
-      <c r="D5" s="330"/>
+      <c r="D5" s="327"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="330" t="s">
+      <c r="F5" s="327" t="s">
         <v>245</v>
       </c>
-      <c r="G5" s="330"/>
+      <c r="G5" s="327"/>
       <c r="H5" s="230">
         <v>0.5</v>
       </c>
@@ -9058,24 +9058,24 @@
       <c r="J5" s="289" t="s">
         <v>244</v>
       </c>
-      <c r="K5" s="330"/>
-      <c r="L5" s="330"/>
-      <c r="M5" s="330"/>
-      <c r="N5" s="330"/>
+      <c r="K5" s="327"/>
+      <c r="L5" s="327"/>
+      <c r="M5" s="327"/>
+      <c r="N5" s="327"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="C6" s="330" t="s">
+      <c r="C6" s="327" t="s">
         <v>247</v>
       </c>
-      <c r="D6" s="330"/>
+      <c r="D6" s="327"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="330" t="s">
+      <c r="F6" s="327" t="s">
         <v>248</v>
       </c>
-      <c r="G6" s="330"/>
+      <c r="G6" s="327"/>
       <c r="H6" s="230">
         <v>0.1</v>
       </c>
@@ -9083,26 +9083,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="289"/>
-      <c r="K6" s="330"/>
-      <c r="L6" s="330"/>
-      <c r="M6" s="330"/>
-      <c r="N6" s="330"/>
+      <c r="K6" s="327"/>
+      <c r="L6" s="327"/>
+      <c r="M6" s="327"/>
+      <c r="N6" s="327"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="77" t="s">
         <v>249</v>
       </c>
-      <c r="C7" s="331">
+      <c r="C7" s="332">
         <v>10000</v>
       </c>
-      <c r="D7" s="331"/>
+      <c r="D7" s="332"/>
       <c r="E7" s="229" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="330" t="s">
+      <c r="F7" s="327" t="s">
         <v>251</v>
       </c>
-      <c r="G7" s="330"/>
+      <c r="G7" s="327"/>
       <c r="H7" s="230">
         <v>0.2</v>
       </c>
@@ -9110,18 +9110,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="289"/>
-      <c r="K7" s="330"/>
-      <c r="L7" s="330"/>
-      <c r="M7" s="330"/>
-      <c r="N7" s="330"/>
+      <c r="K7" s="327"/>
+      <c r="L7" s="327"/>
+      <c r="M7" s="327"/>
+      <c r="N7" s="327"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="330" t="s">
+      <c r="F8" s="327" t="s">
         <v>252</v>
       </c>
-      <c r="G8" s="330"/>
+      <c r="G8" s="327"/>
       <c r="H8" s="230">
         <v>0.1</v>
       </c>
@@ -9129,18 +9129,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="289"/>
-      <c r="K8" s="330"/>
-      <c r="L8" s="330"/>
-      <c r="M8" s="330"/>
-      <c r="N8" s="330"/>
+      <c r="K8" s="327"/>
+      <c r="L8" s="327"/>
+      <c r="M8" s="327"/>
+      <c r="N8" s="327"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="22"/>
       <c r="E9" s="56"/>
-      <c r="F9" s="330" t="s">
+      <c r="F9" s="327" t="s">
         <v>253</v>
       </c>
-      <c r="G9" s="330"/>
+      <c r="G9" s="327"/>
       <c r="H9" s="230">
         <v>0.1</v>
       </c>
@@ -9148,10 +9148,10 @@
         <v>1000</v>
       </c>
       <c r="J9" s="289"/>
-      <c r="K9" s="330"/>
-      <c r="L9" s="330"/>
-      <c r="M9" s="330"/>
-      <c r="N9" s="330"/>
+      <c r="K9" s="327"/>
+      <c r="L9" s="327"/>
+      <c r="M9" s="327"/>
+      <c r="N9" s="327"/>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
@@ -10237,12 +10237,12 @@
       <c r="W45" s="21"/>
     </row>
     <row r="46" spans="2:23" s="89" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="327" t="s">
+      <c r="B46" s="329" t="s">
         <v>233</v>
       </c>
-      <c r="C46" s="327"/>
-      <c r="D46" s="327"/>
-      <c r="E46" s="327"/>
+      <c r="C46" s="329"/>
+      <c r="D46" s="329"/>
+      <c r="E46" s="329"/>
       <c r="F46" s="219">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10406,16 +10406,16 @@
       <c r="R55" s="24"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="328" t="s">
+      <c r="B56" s="330" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="329"/>
-      <c r="D56" s="329"/>
-      <c r="E56" s="329"/>
-      <c r="F56" s="329"/>
-      <c r="G56" s="329"/>
-      <c r="H56" s="329"/>
-      <c r="I56" s="329"/>
+      <c r="C56" s="331"/>
+      <c r="D56" s="331"/>
+      <c r="E56" s="331"/>
+      <c r="F56" s="331"/>
+      <c r="G56" s="331"/>
+      <c r="H56" s="331"/>
+      <c r="I56" s="331"/>
       <c r="J56" s="173"/>
       <c r="K56" s="173"/>
       <c r="L56" s="173"/>
@@ -10429,16 +10429,6 @@
   </sheetData>
   <autoFilter ref="B12:E12" xr:uid="{F0215733-3491-41E7-AEDA-44D9E214180D}"/>
   <mergeCells count="19">
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="C4:D4"/>
@@ -10448,6 +10438,16 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C10">
@@ -43020,21 +43020,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005104B4C06FD53E4DA82687A05841D03F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f48deddc6bffdc45fb3ed0ec71e33c6c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7dc5af80-ab8f-4cff-b7cb-3463b3238b39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a8808579f8fa9f9643be1385777e037d" ns2:_="">
     <xsd:import namespace="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
@@ -43208,24 +43193,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4453D5CC-2F3C-48AA-8382-954EB2322467}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794A36B1-E557-480A-80A5-281FC452AC8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F36A1B76-9E34-462B-9C68-1BC8027D2211}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43243,6 +43226,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794A36B1-E557-480A-80A5-281FC452AC8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4453D5CC-2F3C-48AA-8382-954EB2322467}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{040b5de6-6e2e-46f2-bca1-507eb809bbf7}" enabled="1" method="Privileged" siteId="{56d7daaa-b378-45b3-aa11-af9402b401b9}" contentBits="0" removed="0"/>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.38-ep1\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-ep2\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359449EC-3436-4D92-9A48-D931A550B9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AE00AE-FEE9-413F-A984-A9CE5A16E86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,7 +1123,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:12:49 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:29:18 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-ep2\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.40-ep3\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AE00AE-FEE9-413F-A984-A9CE5A16E86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF60F04-87A1-434F-BDDA-F5CAD84520E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,7 +1123,7 @@
     <t>Sopore especializado</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:29:18 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:50:02 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>
@@ -3072,13 +3072,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3088,9 +3081,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="D4" s="315"/>
       <c r="E4" s="22"/>
-      <c r="F4" s="328" t="s">
+      <c r="F4" s="332" t="s">
         <v>238</v>
       </c>
       <c r="G4" s="333"/>
@@ -9029,26 +9029,26 @@
       <c r="J4" s="228" t="s">
         <v>241</v>
       </c>
-      <c r="K4" s="328" t="s">
+      <c r="K4" s="332" t="s">
         <v>242</v>
       </c>
-      <c r="L4" s="328"/>
-      <c r="M4" s="328"/>
-      <c r="N4" s="328"/>
+      <c r="L4" s="332"/>
+      <c r="M4" s="332"/>
+      <c r="N4" s="332"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="77" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="327" t="s">
+      <c r="C5" s="330" t="s">
         <v>244</v>
       </c>
-      <c r="D5" s="327"/>
+      <c r="D5" s="330"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="327" t="s">
+      <c r="F5" s="330" t="s">
         <v>245</v>
       </c>
-      <c r="G5" s="327"/>
+      <c r="G5" s="330"/>
       <c r="H5" s="230">
         <v>0.5</v>
       </c>
@@ -9058,24 +9058,24 @@
       <c r="J5" s="289" t="s">
         <v>244</v>
       </c>
-      <c r="K5" s="327"/>
-      <c r="L5" s="327"/>
-      <c r="M5" s="327"/>
-      <c r="N5" s="327"/>
+      <c r="K5" s="330"/>
+      <c r="L5" s="330"/>
+      <c r="M5" s="330"/>
+      <c r="N5" s="330"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="C6" s="327" t="s">
+      <c r="C6" s="330" t="s">
         <v>247</v>
       </c>
-      <c r="D6" s="327"/>
+      <c r="D6" s="330"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="327" t="s">
+      <c r="F6" s="330" t="s">
         <v>248</v>
       </c>
-      <c r="G6" s="327"/>
+      <c r="G6" s="330"/>
       <c r="H6" s="230">
         <v>0.1</v>
       </c>
@@ -9083,26 +9083,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="289"/>
-      <c r="K6" s="327"/>
-      <c r="L6" s="327"/>
-      <c r="M6" s="327"/>
-      <c r="N6" s="327"/>
+      <c r="K6" s="330"/>
+      <c r="L6" s="330"/>
+      <c r="M6" s="330"/>
+      <c r="N6" s="330"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="77" t="s">
         <v>249</v>
       </c>
-      <c r="C7" s="332">
+      <c r="C7" s="331">
         <v>10000</v>
       </c>
-      <c r="D7" s="332"/>
+      <c r="D7" s="331"/>
       <c r="E7" s="229" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="327" t="s">
+      <c r="F7" s="330" t="s">
         <v>251</v>
       </c>
-      <c r="G7" s="327"/>
+      <c r="G7" s="330"/>
       <c r="H7" s="230">
         <v>0.2</v>
       </c>
@@ -9110,18 +9110,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="289"/>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
+      <c r="K7" s="330"/>
+      <c r="L7" s="330"/>
+      <c r="M7" s="330"/>
+      <c r="N7" s="330"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="327" t="s">
+      <c r="F8" s="330" t="s">
         <v>252</v>
       </c>
-      <c r="G8" s="327"/>
+      <c r="G8" s="330"/>
       <c r="H8" s="230">
         <v>0.1</v>
       </c>
@@ -9129,18 +9129,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="289"/>
-      <c r="K8" s="327"/>
-      <c r="L8" s="327"/>
-      <c r="M8" s="327"/>
-      <c r="N8" s="327"/>
+      <c r="K8" s="330"/>
+      <c r="L8" s="330"/>
+      <c r="M8" s="330"/>
+      <c r="N8" s="330"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="22"/>
       <c r="E9" s="56"/>
-      <c r="F9" s="327" t="s">
+      <c r="F9" s="330" t="s">
         <v>253</v>
       </c>
-      <c r="G9" s="327"/>
+      <c r="G9" s="330"/>
       <c r="H9" s="230">
         <v>0.1</v>
       </c>
@@ -9148,10 +9148,10 @@
         <v>1000</v>
       </c>
       <c r="J9" s="289"/>
-      <c r="K9" s="327"/>
-      <c r="L9" s="327"/>
-      <c r="M9" s="327"/>
-      <c r="N9" s="327"/>
+      <c r="K9" s="330"/>
+      <c r="L9" s="330"/>
+      <c r="M9" s="330"/>
+      <c r="N9" s="330"/>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
@@ -10237,12 +10237,12 @@
       <c r="W45" s="21"/>
     </row>
     <row r="46" spans="2:23" s="89" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="329" t="s">
+      <c r="B46" s="327" t="s">
         <v>233</v>
       </c>
-      <c r="C46" s="329"/>
-      <c r="D46" s="329"/>
-      <c r="E46" s="329"/>
+      <c r="C46" s="327"/>
+      <c r="D46" s="327"/>
+      <c r="E46" s="327"/>
       <c r="F46" s="219">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10406,16 +10406,16 @@
       <c r="R55" s="24"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="330" t="s">
+      <c r="B56" s="328" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="331"/>
-      <c r="D56" s="331"/>
-      <c r="E56" s="331"/>
-      <c r="F56" s="331"/>
-      <c r="G56" s="331"/>
-      <c r="H56" s="331"/>
-      <c r="I56" s="331"/>
+      <c r="C56" s="329"/>
+      <c r="D56" s="329"/>
+      <c r="E56" s="329"/>
+      <c r="F56" s="329"/>
+      <c r="G56" s="329"/>
+      <c r="H56" s="329"/>
+      <c r="I56" s="329"/>
       <c r="J56" s="173"/>
       <c r="K56" s="173"/>
       <c r="L56" s="173"/>
@@ -10429,6 +10429,16 @@
   </sheetData>
   <autoFilter ref="B12:E12" xr:uid="{F0215733-3491-41E7-AEDA-44D9E214180D}"/>
   <mergeCells count="19">
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="C4:D4"/>
@@ -10438,16 +10448,6 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C10">
@@ -43020,6 +43020,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005104B4C06FD53E4DA82687A05841D03F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f48deddc6bffdc45fb3ed0ec71e33c6c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7dc5af80-ab8f-4cff-b7cb-3463b3238b39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a8808579f8fa9f9643be1385777e037d" ns2:_="">
     <xsd:import namespace="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
@@ -43193,22 +43208,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4453D5CC-2F3C-48AA-8382-954EB2322467}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794A36B1-E557-480A-80A5-281FC452AC8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F36A1B76-9E34-462B-9C68-1BC8027D2211}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43226,23 +43243,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794A36B1-E557-480A-80A5-281FC452AC8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4453D5CC-2F3C-48AA-8382-954EB2322467}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{040b5de6-6e2e-46f2-bca1-507eb809bbf7}" enabled="1" method="Privileged" siteId="{56d7daaa-b378-45b3-aa11-af9402b401b9}" contentBits="0" removed="0"/>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.42-ep4\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.55-ep5\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBFD36F-C143-4626-9695-30AC36614281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C655245-B8E8-4BD2-A880-F76F42DA43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1126,7 +1126,7 @@
     <t/>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 03:09:29 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 04:28:50 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_AT_20251160543.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.55-ep5\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.56-ep6\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C655245-B8E8-4BD2-A880-F76F42DA43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A4FD6B-354F-45C0-9854-A6C05D165D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="669" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1126,7 +1126,7 @@
     <t/>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 04:28:50 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 04:40:41 | PPO=20251160543_PPO_CEducación_AMS_SI_Lote 2_v01.xlsm | NumeroSF=20251160543 | Tipo=AT | Campos PPO=8 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | AT: tarifas de venta reescaladas proporcionalmente para cuadrar venta facturable con importe total de venta del proyecto: 465.000,00 EUR. Se conservan horas, costes y perfiles; solo se ajusta tarifa de venta. Revisión requerida si negocio exige tarifa literal por linea PPO.</t>
   </si>
 </sst>
 </file>
